--- a/igzo_4t2c_retention/4t2c_map_chip6_4t2c_a_mbl-2p50_0902_155745.xlsx
+++ b/igzo_4t2c_retention/4t2c_map_chip6_4t2c_a_mbl-2p50_0902_155745.xlsx
@@ -567,10 +567,10 @@
         <v>2.949939</v>
       </c>
       <c r="P2" t="n">
-        <v>2.94993894993895e-06</v>
+        <v>0.000109256998</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.949939</v>
+        <v>109.257</v>
       </c>
       <c r="R2" t="n">
         <v>577.05</v>
@@ -632,10 +632,10 @@
         <v>2.915751</v>
       </c>
       <c r="P3" t="n">
-        <v>2.915750915750915e-06</v>
+        <v>0.000107990775</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.915751</v>
+        <v>107.990778</v>
       </c>
       <c r="R3" t="n">
         <v>395.33</v>
@@ -697,10 +697,10 @@
         <v>2.881563</v>
       </c>
       <c r="P4" t="n">
-        <v>2.881562881562881e-06</v>
+        <v>0.000106724551</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.881563</v>
+        <v>106.724556</v>
       </c>
       <c r="R4" t="n">
         <v>586.62</v>
@@ -762,10 +762,10 @@
         <v>2.845747</v>
       </c>
       <c r="P5" t="n">
-        <v>2.845746845746846e-06</v>
+        <v>0.000105398031</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.845747</v>
+        <v>105.398037</v>
       </c>
       <c r="R5" t="n">
         <v>577.72</v>
@@ -827,10 +827,10 @@
         <v>2.811966</v>
       </c>
       <c r="P6" t="n">
-        <v>2.811965811965812e-06</v>
+        <v>0.000104146882</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.811966</v>
+        <v>104.146889</v>
       </c>
       <c r="R6" t="n">
         <v>514.61</v>
@@ -892,10 +892,10 @@
         <v>2.778185</v>
       </c>
       <c r="P7" t="n">
-        <v>2.778184778184779e-06</v>
+        <v>0.000102895733</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.778185</v>
+        <v>102.895741</v>
       </c>
       <c r="R7" t="n">
         <v>575.91</v>
@@ -957,10 +957,10 @@
         <v>2.749695</v>
       </c>
       <c r="P8" t="n">
-        <v>2.74969474969475e-06</v>
+        <v>0.000101840546</v>
       </c>
       <c r="Q8" t="n">
-        <v>2.749695</v>
+        <v>101.840556</v>
       </c>
       <c r="R8" t="n">
         <v>516.62</v>
@@ -1022,10 +1022,10 @@
         <v>2.715507</v>
       </c>
       <c r="P9" t="n">
-        <v>2.715506715506715e-06</v>
+        <v>0.000100574323</v>
       </c>
       <c r="Q9" t="n">
-        <v>2.715507</v>
+        <v>100.574333</v>
       </c>
       <c r="R9" t="n">
         <v>454.19</v>
@@ -1087,10 +1087,10 @@
         <v>2.689459</v>
       </c>
       <c r="P10" t="n">
-        <v>2.689458689458689e-06</v>
+        <v>9.96095811e-05</v>
       </c>
       <c r="Q10" t="n">
-        <v>2.689459</v>
+        <v>99.6095926</v>
       </c>
       <c r="R10" t="n">
         <v>567.33</v>
@@ -1152,10 +1152,10 @@
         <v>2.656492</v>
       </c>
       <c r="P11" t="n">
-        <v>2.656491656491656e-06</v>
+        <v>9.83885799e-05</v>
       </c>
       <c r="Q11" t="n">
-        <v>2.656492</v>
+        <v>98.3885926</v>
       </c>
       <c r="R11" t="n">
         <v>453.69</v>
@@ -1217,10 +1217,10 @@
         <v>2.636549</v>
       </c>
       <c r="P12" t="n">
-        <v>2.636548636548637e-06</v>
+        <v>9.76499495e-05</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.636549</v>
+        <v>97.649963</v>
       </c>
       <c r="R12" t="n">
         <v>516.3</v>
@@ -1282,10 +1282,10 @@
         <v>2.612943</v>
       </c>
       <c r="P13" t="n">
-        <v>2.612942612942613e-06</v>
+        <v>9.67756523e-05</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.612943</v>
+        <v>96.7756667</v>
       </c>
       <c r="R13" t="n">
         <v>577.98</v>
@@ -1347,10 +1347,10 @@
         <v>2.586895</v>
       </c>
       <c r="P14" t="n">
-        <v>2.586894586894587e-06</v>
+        <v>9.58109106e-05</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.586895</v>
+        <v>95.8109259</v>
       </c>
       <c r="R14" t="n">
         <v>455.88</v>
@@ -1412,10 +1412,10 @@
         <v>2.559219</v>
       </c>
       <c r="P15" t="n">
-        <v>2.559218559218559e-06</v>
+        <v>9.47858726e-05</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.559219</v>
+        <v>94.7858889</v>
       </c>
       <c r="R15" t="n">
         <v>574.48</v>
@@ -1477,10 +1477,10 @@
         <v>2.538462</v>
       </c>
       <c r="P16" t="n">
-        <v>2.538461538461538e-06</v>
+        <v>9.4017094e-05</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.538462</v>
+        <v>94.0171111</v>
       </c>
       <c r="R16" t="n">
         <v>514.08</v>
@@ -1542,10 +1542,10 @@
         <v>2.51974</v>
       </c>
       <c r="P17" t="n">
-        <v>2.51973951973952e-06</v>
+        <v>9.33236859e-05</v>
       </c>
       <c r="Q17" t="n">
-        <v>2.51974</v>
+        <v>93.3237037</v>
       </c>
       <c r="R17" t="n">
         <v>453.07</v>
@@ -1607,10 +1607,10 @@
         <v>2.503867</v>
       </c>
       <c r="P18" t="n">
-        <v>2.503866503866504e-06</v>
+        <v>9.27357964e-05</v>
       </c>
       <c r="Q18" t="n">
-        <v>2.503867</v>
+        <v>92.7358148</v>
       </c>
       <c r="R18" t="n">
         <v>458.88</v>
@@ -1672,10 +1672,10 @@
         <v>2.496947</v>
       </c>
       <c r="P19" t="n">
-        <v>2.496947496947497e-06</v>
+        <v>9.24795369e-05</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.496947</v>
+        <v>92.4795185</v>
       </c>
       <c r="R19" t="n">
         <v>528.3</v>
@@ -1737,10 +1737,10 @@
         <v>2.478632</v>
       </c>
       <c r="P20" t="n">
-        <v>2.478632478632479e-06</v>
+        <v>9.18012029e-05</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.478632</v>
+        <v>91.8011852</v>
       </c>
       <c r="R20" t="n">
         <v>514.0700000000001</v>
@@ -1802,10 +1802,10 @@
         <v>2.461945</v>
       </c>
       <c r="P21" t="n">
-        <v>2.461945461945462e-06</v>
+        <v>9.11831653e-05</v>
       </c>
       <c r="Q21" t="n">
-        <v>2.461945</v>
+        <v>91.1831481</v>
       </c>
       <c r="R21" t="n">
         <v>514.61</v>
@@ -1867,10 +1867,10 @@
         <v>2.450142</v>
       </c>
       <c r="P22" t="n">
-        <v>2.45014245014245e-06</v>
+        <v>9.07460167e-05</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.450142</v>
+        <v>90.746</v>
       </c>
       <c r="R22" t="n">
         <v>572.04</v>
@@ -1932,10 +1932,10 @@
         <v>2.439967</v>
       </c>
       <c r="P23" t="n">
-        <v>2.43996743996744e-06</v>
+        <v>9.03691644e-05</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.439967</v>
+        <v>90.3691481</v>
       </c>
       <c r="R23" t="n">
         <v>576.29</v>
@@ -1997,10 +1997,10 @@
         <v>2.428978</v>
       </c>
       <c r="P24" t="n">
-        <v>2.428978428978429e-06</v>
+        <v>8.9962164e-05</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.428978</v>
+        <v>89.9621481</v>
       </c>
       <c r="R24" t="n">
         <v>452.93</v>
@@ -2062,10 +2062,10 @@
         <v>2.420024</v>
       </c>
       <c r="P25" t="n">
-        <v>2.42002442002442e-06</v>
+        <v>8.96305341e-05</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.420024</v>
+        <v>89.6305185</v>
       </c>
       <c r="R25" t="n">
         <v>531</v>
@@ -2127,10 +2127,10 @@
         <v>2.415954</v>
       </c>
       <c r="P26" t="n">
-        <v>2.415954415954416e-06</v>
+        <v>8.94797932e-05</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.415954</v>
+        <v>89.4797778</v>
       </c>
       <c r="R26" t="n">
         <v>514.86</v>
@@ -2192,10 +2192,10 @@
         <v>2.407814</v>
       </c>
       <c r="P27" t="n">
-        <v>2.407814407814408e-06</v>
+        <v>8.91783114e-05</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.407814</v>
+        <v>89.1782963</v>
       </c>
       <c r="R27" t="n">
         <v>512.2</v>
@@ -2257,10 +2257,10 @@
         <v>2.406593</v>
       </c>
       <c r="P28" t="n">
-        <v>2.406593406593407e-06</v>
+        <v>8.91330891e-05</v>
       </c>
       <c r="Q28" t="n">
-        <v>2.406593</v>
+        <v>89.1330741</v>
       </c>
       <c r="R28" t="n">
         <v>455.97</v>
@@ -2322,10 +2322,10 @@
         <v>2.40293</v>
       </c>
       <c r="P29" t="n">
-        <v>2.402930402930403e-06</v>
+        <v>8.89974223e-05</v>
       </c>
       <c r="Q29" t="n">
-        <v>2.40293</v>
+        <v>88.9974074</v>
       </c>
       <c r="R29" t="n">
         <v>466.02</v>
@@ -2387,10 +2387,10 @@
         <v>2.40293</v>
       </c>
       <c r="P30" t="n">
-        <v>2.402930402930403e-06</v>
+        <v>8.89974223e-05</v>
       </c>
       <c r="Q30" t="n">
-        <v>2.40293</v>
+        <v>88.9974074</v>
       </c>
       <c r="R30" t="n">
         <v>573.74</v>
@@ -2452,10 +2452,10 @@
         <v>2.399674</v>
       </c>
       <c r="P31" t="n">
-        <v>2.399674399674399e-06</v>
+        <v>8.88768296e-05</v>
       </c>
       <c r="Q31" t="n">
-        <v>2.399674</v>
+        <v>88.8768148</v>
       </c>
       <c r="R31" t="n">
         <v>457.07</v>
@@ -2517,10 +2517,10 @@
         <v>2.404558</v>
       </c>
       <c r="P32" t="n">
-        <v>2.404558404558404e-06</v>
+        <v>8.90577187e-05</v>
       </c>
       <c r="Q32" t="n">
-        <v>2.404558</v>
+        <v>89.0577037</v>
       </c>
       <c r="R32" t="n">
         <v>469.86</v>
@@ -2582,10 +2582,10 @@
         <v>2.792023</v>
       </c>
       <c r="P33" t="n">
-        <v>2.792022792022792e-06</v>
+        <v>0.000103408252</v>
       </c>
       <c r="Q33" t="n">
-        <v>2.792023</v>
+        <v>103.408259</v>
       </c>
       <c r="R33" t="n">
         <v>514.8099999999999</v>
@@ -2647,10 +2647,10 @@
         <v>2.75173</v>
       </c>
       <c r="P34" t="n">
-        <v>2.751729751729751e-06</v>
+        <v>0.000101915917</v>
       </c>
       <c r="Q34" t="n">
-        <v>2.75173</v>
+        <v>101.915926</v>
       </c>
       <c r="R34" t="n">
         <v>458.55</v>
@@ -2712,10 +2712,10 @@
         <v>2.715914</v>
       </c>
       <c r="P35" t="n">
-        <v>2.715913715913716e-06</v>
+        <v>0.000100589397</v>
       </c>
       <c r="Q35" t="n">
-        <v>2.715914</v>
+        <v>100.589407</v>
       </c>
       <c r="R35" t="n">
         <v>573.53</v>
@@ -2777,10 +2777,10 @@
         <v>2.677249</v>
       </c>
       <c r="P36" t="n">
-        <v>2.677248677248677e-06</v>
+        <v>9.91573584e-05</v>
       </c>
       <c r="Q36" t="n">
-        <v>2.677249</v>
+        <v>99.1573704</v>
       </c>
       <c r="R36" t="n">
         <v>516.47</v>
@@ -2842,10 +2842,10 @@
         <v>2.647131</v>
       </c>
       <c r="P37" t="n">
-        <v>2.647130647130647e-06</v>
+        <v>9.80418758e-05</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.647131</v>
+        <v>98.0418889</v>
       </c>
       <c r="R37" t="n">
         <v>512.9400000000001</v>
@@ -2907,10 +2907,10 @@
         <v>2.611315</v>
       </c>
       <c r="P38" t="n">
-        <v>2.611314611314611e-06</v>
+        <v>9.6715356e-05</v>
       </c>
       <c r="Q38" t="n">
-        <v>2.611315</v>
+        <v>96.7153704</v>
       </c>
       <c r="R38" t="n">
         <v>513.1799999999999</v>
@@ -2972,10 +2972,10 @@
         <v>2.573871</v>
       </c>
       <c r="P39" t="n">
-        <v>2.573870573870574e-06</v>
+        <v>9.53285398e-05</v>
       </c>
       <c r="Q39" t="n">
-        <v>2.573871</v>
+        <v>95.3285556</v>
       </c>
       <c r="R39" t="n">
         <v>575.14</v>
@@ -3037,10 +3037,10 @@
         <v>2.538462</v>
       </c>
       <c r="P40" t="n">
-        <v>2.538461538461538e-06</v>
+        <v>9.4017094e-05</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.538462</v>
+        <v>94.0171111</v>
       </c>
       <c r="R40" t="n">
         <v>458.72</v>
@@ -3102,10 +3102,10 @@
         <v>2.505902</v>
       </c>
       <c r="P41" t="n">
-        <v>2.505901505901506e-06</v>
+        <v>9.28111669e-05</v>
       </c>
       <c r="Q41" t="n">
-        <v>2.505902</v>
+        <v>92.8111852</v>
       </c>
       <c r="R41" t="n">
         <v>511.81</v>
@@ -3167,10 +3167,10 @@
         <v>2.481074</v>
       </c>
       <c r="P42" t="n">
-        <v>2.481074481074481e-06</v>
+        <v>9.18916474e-05</v>
       </c>
       <c r="Q42" t="n">
-        <v>2.481074</v>
+        <v>91.8916296</v>
       </c>
       <c r="R42" t="n">
         <v>515.3099999999999</v>
@@ -3232,10 +3232,10 @@
         <v>2.447293</v>
       </c>
       <c r="P43" t="n">
-        <v>2.447293447293447e-06</v>
+        <v>9.0640498e-05</v>
       </c>
       <c r="Q43" t="n">
-        <v>2.447293</v>
+        <v>90.6404815</v>
       </c>
       <c r="R43" t="n">
         <v>512.01</v>
@@ -3297,10 +3297,10 @@
         <v>2.422873</v>
       </c>
       <c r="P44" t="n">
-        <v>2.422873422873423e-06</v>
+        <v>8.97360527e-05</v>
       </c>
       <c r="Q44" t="n">
-        <v>2.422873</v>
+        <v>89.736037</v>
       </c>
       <c r="R44" t="n">
         <v>516.86</v>
@@ -3362,10 +3362,10 @@
         <v>2.39479</v>
       </c>
       <c r="P45" t="n">
-        <v>2.394790394790394e-06</v>
+        <v>8.86959405e-05</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.39479</v>
+        <v>88.6959259</v>
       </c>
       <c r="R45" t="n">
         <v>515.01</v>
@@ -3427,10 +3427,10 @@
         <v>2.367114</v>
       </c>
       <c r="P46" t="n">
-        <v>2.367114367114367e-06</v>
+        <v>8.76709025e-05</v>
       </c>
       <c r="Q46" t="n">
-        <v>2.367114</v>
+        <v>87.6708889</v>
       </c>
       <c r="R46" t="n">
         <v>516.97</v>
@@ -3492,10 +3492,10 @@
         <v>2.343101</v>
       </c>
       <c r="P47" t="n">
-        <v>2.343101343101343e-06</v>
+        <v>8.67815312e-05</v>
       </c>
       <c r="Q47" t="n">
-        <v>2.343101</v>
+        <v>86.7815185</v>
       </c>
       <c r="R47" t="n">
         <v>519.85</v>
@@ -3557,10 +3557,10 @@
         <v>2.323158</v>
       </c>
       <c r="P48" t="n">
-        <v>2.323158323158323e-06</v>
+        <v>8.60429009e-05</v>
       </c>
       <c r="Q48" t="n">
-        <v>2.323158</v>
+        <v>86.0428889</v>
       </c>
       <c r="R48" t="n">
         <v>450.97</v>
@@ -3622,10 +3622,10 @@
         <v>2.30118</v>
       </c>
       <c r="P49" t="n">
-        <v>2.301180301180301e-06</v>
+        <v>8.52289e-05</v>
       </c>
       <c r="Q49" t="n">
-        <v>2.30118</v>
+        <v>85.2288889</v>
       </c>
       <c r="R49" t="n">
         <v>395.48</v>
@@ -3687,10 +3687,10 @@
         <v>2.280016</v>
       </c>
       <c r="P50" t="n">
-        <v>2.28001628001628e-06</v>
+        <v>8.44450474e-05</v>
       </c>
       <c r="Q50" t="n">
-        <v>2.280016</v>
+        <v>84.445037</v>
       </c>
       <c r="R50" t="n">
         <v>587.7</v>
@@ -3752,10 +3752,10 @@
         <v>2.264143</v>
       </c>
       <c r="P51" t="n">
-        <v>2.264143264143264e-06</v>
+        <v>8.38571579e-05</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.264143</v>
+        <v>83.8571481</v>
       </c>
       <c r="R51" t="n">
         <v>516.62</v>
@@ -3817,10 +3817,10 @@
         <v>2.245014</v>
       </c>
       <c r="P52" t="n">
-        <v>2.245014245014245e-06</v>
+        <v>8.31486757e-05</v>
       </c>
       <c r="Q52" t="n">
-        <v>2.245014</v>
+        <v>83.1486667</v>
       </c>
       <c r="R52" t="n">
         <v>514.38</v>
@@ -3882,10 +3882,10 @@
         <v>2.225071</v>
       </c>
       <c r="P53" t="n">
-        <v>2.225071225071225e-06</v>
+        <v>8.24100454e-05</v>
       </c>
       <c r="Q53" t="n">
-        <v>2.225071</v>
+        <v>82.410037</v>
       </c>
       <c r="R53" t="n">
         <v>516.14</v>
@@ -3947,10 +3947,10 @@
         <v>2.21571</v>
       </c>
       <c r="P54" t="n">
-        <v>2.215710215710216e-06</v>
+        <v>8.20633413e-05</v>
       </c>
       <c r="Q54" t="n">
-        <v>2.21571</v>
+        <v>82.0633333</v>
       </c>
       <c r="R54" t="n">
         <v>573.89</v>
@@ -4012,10 +4012,10 @@
         <v>2.205535</v>
       </c>
       <c r="P55" t="n">
-        <v>2.205535205535205e-06</v>
+        <v>8.16864891e-05</v>
       </c>
       <c r="Q55" t="n">
-        <v>2.205535</v>
+        <v>81.6864815</v>
       </c>
       <c r="R55" t="n">
         <v>516.79</v>
@@ -4077,10 +4077,10 @@
         <v>2.195767</v>
       </c>
       <c r="P56" t="n">
-        <v>2.195767195767196e-06</v>
+        <v>8.1324711e-05</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.195767</v>
+        <v>81.3247037</v>
       </c>
       <c r="R56" t="n">
         <v>451</v>
@@ -4142,10 +4142,10 @@
         <v>2.189255</v>
       </c>
       <c r="P57" t="n">
-        <v>2.189255189255189e-06</v>
+        <v>8.10835255e-05</v>
       </c>
       <c r="Q57" t="n">
-        <v>2.189255</v>
+        <v>81.0835185</v>
       </c>
       <c r="R57" t="n">
         <v>577.24</v>
@@ -4207,10 +4207,10 @@
         <v>2.186406</v>
       </c>
       <c r="P58" t="n">
-        <v>2.186406186406186e-06</v>
+        <v>8.09780069e-05</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.186406</v>
+        <v>80.978</v>
       </c>
       <c r="R58" t="n">
         <v>575.73</v>
@@ -4272,10 +4272,10 @@
         <v>2.186406</v>
       </c>
       <c r="P59" t="n">
-        <v>2.186406186406186e-06</v>
+        <v>8.09780069e-05</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.186406</v>
+        <v>80.978</v>
       </c>
       <c r="R59" t="n">
         <v>514.02</v>
@@ -4337,10 +4337,10 @@
         <v>2.186406</v>
       </c>
       <c r="P60" t="n">
-        <v>2.186406186406186e-06</v>
+        <v>8.09780069e-05</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.186406</v>
+        <v>80.978</v>
       </c>
       <c r="R60" t="n">
         <v>509.1</v>
@@ -4402,10 +4402,10 @@
         <v>2.188034</v>
       </c>
       <c r="P61" t="n">
-        <v>2.188034188034188e-06</v>
+        <v>8.10383033e-05</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.188034</v>
+        <v>81.0382963</v>
       </c>
       <c r="R61" t="n">
         <v>517.92</v>
@@ -4467,10 +4467,10 @@
         <v>2.188034</v>
       </c>
       <c r="P62" t="n">
-        <v>2.188034188034188e-06</v>
+        <v>8.10383033e-05</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.188034</v>
+        <v>81.0382963</v>
       </c>
       <c r="R62" t="n">
         <v>454.25</v>
@@ -4532,10 +4532,10 @@
         <v>2.194546</v>
       </c>
       <c r="P63" t="n">
-        <v>2.194546194546195e-06</v>
+        <v>8.12794887e-05</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.194546</v>
+        <v>81.2794815</v>
       </c>
       <c r="R63" t="n">
         <v>576.4299999999999</v>
@@ -4597,10 +4597,10 @@
         <v>2.589337</v>
       </c>
       <c r="P64" t="n">
-        <v>2.589336589336589e-06</v>
+        <v>9.59013552e-05</v>
       </c>
       <c r="Q64" t="n">
-        <v>2.589337</v>
+        <v>95.9013704</v>
       </c>
       <c r="R64" t="n">
         <v>584.7</v>
@@ -4662,10 +4662,10 @@
         <v>2.552707</v>
       </c>
       <c r="P65" t="n">
-        <v>2.552706552706553e-06</v>
+        <v>9.45446871e-05</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.552707</v>
+        <v>94.5447037</v>
       </c>
       <c r="R65" t="n">
         <v>517</v>
@@ -4727,10 +4727,10 @@
         <v>2.508751</v>
       </c>
       <c r="P66" t="n">
-        <v>2.508750508750509e-06</v>
+        <v>9.29166855e-05</v>
       </c>
       <c r="Q66" t="n">
-        <v>2.508751</v>
+        <v>92.9167037</v>
       </c>
       <c r="R66" t="n">
         <v>516.34</v>
@@ -4792,10 +4792,10 @@
         <v>2.47619</v>
       </c>
       <c r="P67" t="n">
-        <v>2.476190476190476e-06</v>
+        <v>9.17107584e-05</v>
       </c>
       <c r="Q67" t="n">
-        <v>2.47619</v>
+        <v>91.7107407</v>
       </c>
       <c r="R67" t="n">
         <v>570.08</v>
@@ -4857,10 +4857,10 @@
         <v>2.432234</v>
       </c>
       <c r="P68" t="n">
-        <v>2.432234432234432e-06</v>
+        <v>9.00827567e-05</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.432234</v>
+        <v>90.0827407</v>
       </c>
       <c r="R68" t="n">
         <v>515.08</v>
@@ -4922,10 +4922,10 @@
         <v>2.393976</v>
       </c>
       <c r="P69" t="n">
-        <v>2.393976393976394e-06</v>
+        <v>8.86657924e-05</v>
       </c>
       <c r="Q69" t="n">
-        <v>2.393976</v>
+        <v>88.6657778</v>
       </c>
       <c r="R69" t="n">
         <v>578.61</v>
@@ -4987,10 +4987,10 @@
         <v>2.354904</v>
       </c>
       <c r="P70" t="n">
-        <v>2.354904354904355e-06</v>
+        <v>8.72186798e-05</v>
       </c>
       <c r="Q70" t="n">
-        <v>2.354904</v>
+        <v>87.2186667</v>
       </c>
       <c r="R70" t="n">
         <v>394.32</v>
@@ -5052,10 +5052,10 @@
         <v>2.314204</v>
       </c>
       <c r="P71" t="n">
-        <v>2.314204314204314e-06</v>
+        <v>8.57112709e-05</v>
       </c>
       <c r="Q71" t="n">
-        <v>2.314204</v>
+        <v>85.7112593</v>
       </c>
       <c r="R71" t="n">
         <v>526.5700000000001</v>
@@ -5117,10 +5117,10 @@
         <v>2.278388</v>
       </c>
       <c r="P72" t="n">
-        <v>2.278388278388278e-06</v>
+        <v>8.43847511e-05</v>
       </c>
       <c r="Q72" t="n">
-        <v>2.278388</v>
+        <v>84.3847407</v>
       </c>
       <c r="R72" t="n">
         <v>510.95</v>
@@ -5182,10 +5182,10 @@
         <v>2.243386</v>
       </c>
       <c r="P73" t="n">
-        <v>2.243386243386243e-06</v>
+        <v>8.30883794e-05</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.243386</v>
+        <v>83.0883704</v>
       </c>
       <c r="R73" t="n">
         <v>453.1</v>
@@ -5247,10 +5247,10 @@
         <v>2.205942</v>
       </c>
       <c r="P74" t="n">
-        <v>2.205942205942206e-06</v>
+        <v>8.17015632e-05</v>
       </c>
       <c r="Q74" t="n">
-        <v>2.205942</v>
+        <v>81.7015556</v>
       </c>
       <c r="R74" t="n">
         <v>578.84</v>
@@ -5312,10 +5312,10 @@
         <v>2.178266</v>
       </c>
       <c r="P75" t="n">
-        <v>2.178266178266178e-06</v>
+        <v>8.06765251e-05</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.178266</v>
+        <v>80.6765185</v>
       </c>
       <c r="R75" t="n">
         <v>513.7</v>
@@ -5377,10 +5377,10 @@
         <v>2.14652</v>
       </c>
       <c r="P76" t="n">
-        <v>2.146520146520147e-06</v>
+        <v>7.95007462e-05</v>
       </c>
       <c r="Q76" t="n">
-        <v>2.14652</v>
+        <v>79.5007407</v>
       </c>
       <c r="R76" t="n">
         <v>515.45</v>
@@ -5442,10 +5442,10 @@
         <v>2.115181</v>
       </c>
       <c r="P77" t="n">
-        <v>2.115181115181115e-06</v>
+        <v>7.83400413e-05</v>
       </c>
       <c r="Q77" t="n">
-        <v>2.115181</v>
+        <v>78.340037</v>
       </c>
       <c r="R77" t="n">
         <v>457.89</v>
@@ -5507,10 +5507,10 @@
         <v>2.08954</v>
       </c>
       <c r="P78" t="n">
-        <v>2.08954008954009e-06</v>
+        <v>7.73903737e-05</v>
       </c>
       <c r="Q78" t="n">
-        <v>2.08954</v>
+        <v>77.3903704</v>
       </c>
       <c r="R78" t="n">
         <v>572.72</v>
@@ -5572,10 +5572,10 @@
         <v>2.06105</v>
       </c>
       <c r="P79" t="n">
-        <v>2.061050061050061e-06</v>
+        <v>7.63351874e-05</v>
       </c>
       <c r="Q79" t="n">
-        <v>2.06105</v>
+        <v>76.3351852</v>
       </c>
       <c r="R79" t="n">
         <v>455.23</v>
@@ -5637,10 +5637,10 @@
         <v>2.036223</v>
       </c>
       <c r="P80" t="n">
-        <v>2.036223036223036e-06</v>
+        <v>7.5415668e-05</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.036223</v>
+        <v>75.4156667</v>
       </c>
       <c r="R80" t="n">
         <v>459.18</v>
@@ -5702,10 +5702,10 @@
         <v>2.015059</v>
       </c>
       <c r="P81" t="n">
-        <v>2.015059015059015e-06</v>
+        <v>7.46318154e-05</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.015059</v>
+        <v>74.6318148</v>
       </c>
       <c r="R81" t="n">
         <v>527.77</v>
@@ -5767,10 +5767,10 @@
         <v>2.000407</v>
       </c>
       <c r="P82" t="n">
-        <v>2.000407000407e-06</v>
+        <v>7.40891482e-05</v>
       </c>
       <c r="Q82" t="n">
-        <v>2.000407</v>
+        <v>74.0891481</v>
       </c>
       <c r="R82" t="n">
         <v>578.0599999999999</v>
@@ -5832,10 +5832,10 @@
         <v>1.97558</v>
       </c>
       <c r="P83" t="n">
-        <v>1.975579975579976e-06</v>
+        <v>7.31696287e-05</v>
       </c>
       <c r="Q83" t="n">
-        <v>1.97558</v>
+        <v>73.1696296</v>
       </c>
       <c r="R83" t="n">
         <v>509</v>
@@ -5897,10 +5897,10 @@
         <v>1.96337</v>
       </c>
       <c r="P84" t="n">
-        <v>1.963369963369963e-06</v>
+        <v>7.27174061e-05</v>
       </c>
       <c r="Q84" t="n">
-        <v>1.96337</v>
+        <v>72.7174074</v>
       </c>
       <c r="R84" t="n">
         <v>518.17</v>
@@ -5962,10 +5962,10 @@
         <v>1.95116</v>
       </c>
       <c r="P85" t="n">
-        <v>1.951159951159951e-06</v>
+        <v>7.22651834e-05</v>
       </c>
       <c r="Q85" t="n">
-        <v>1.95116</v>
+        <v>72.2651852</v>
       </c>
       <c r="R85" t="n">
         <v>572.83</v>
@@ -6027,10 +6027,10 @@
         <v>1.945462</v>
       </c>
       <c r="P86" t="n">
-        <v>1.945461945461945e-06</v>
+        <v>7.20541461e-05</v>
       </c>
       <c r="Q86" t="n">
-        <v>1.945462</v>
+        <v>72.0541481</v>
       </c>
       <c r="R86" t="n">
         <v>512.84</v>
@@ -6092,10 +6092,10 @@
         <v>1.937322</v>
       </c>
       <c r="P87" t="n">
-        <v>1.937321937321938e-06</v>
+        <v>7.17526643e-05</v>
       </c>
       <c r="Q87" t="n">
-        <v>1.937322</v>
+        <v>71.7526667</v>
       </c>
       <c r="R87" t="n">
         <v>521</v>
@@ -6157,10 +6157,10 @@
         <v>1.93488</v>
       </c>
       <c r="P88" t="n">
-        <v>1.934879934879935e-06</v>
+        <v>7.16622198e-05</v>
       </c>
       <c r="Q88" t="n">
-        <v>1.93488</v>
+        <v>71.6622222</v>
       </c>
       <c r="R88" t="n">
         <v>511.35</v>
@@ -6222,10 +6222,10 @@
         <v>1.934066</v>
       </c>
       <c r="P89" t="n">
-        <v>1.934065934065934e-06</v>
+        <v>7.16320716e-05</v>
       </c>
       <c r="Q89" t="n">
-        <v>1.934066</v>
+        <v>71.6320741</v>
       </c>
       <c r="R89" t="n">
         <v>457.32</v>
@@ -6287,10 +6287,10 @@
         <v>1.936915</v>
       </c>
       <c r="P90" t="n">
-        <v>1.936914936914937e-06</v>
+        <v>7.17375903e-05</v>
       </c>
       <c r="Q90" t="n">
-        <v>1.936915</v>
+        <v>71.7375926</v>
       </c>
       <c r="R90" t="n">
         <v>573.12</v>
@@ -6352,10 +6352,10 @@
         <v>1.943834</v>
       </c>
       <c r="P91" t="n">
-        <v>1.943833943833944e-06</v>
+        <v>7.19938498e-05</v>
       </c>
       <c r="Q91" t="n">
-        <v>1.943834</v>
+        <v>71.9938519</v>
       </c>
       <c r="R91" t="n">
         <v>516.38</v>
@@ -6417,10 +6417,10 @@
         <v>1.956451</v>
       </c>
       <c r="P92" t="n">
-        <v>1.956450956450956e-06</v>
+        <v>7.24611465e-05</v>
       </c>
       <c r="Q92" t="n">
-        <v>1.956451</v>
+        <v>72.4611481</v>
       </c>
       <c r="R92" t="n">
         <v>515</v>
@@ -6482,10 +6482,10 @@
         <v>1.97151</v>
       </c>
       <c r="P93" t="n">
-        <v>1.971509971509971e-06</v>
+        <v>7.30188878e-05</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.97151</v>
+        <v>73.0188889</v>
       </c>
       <c r="R93" t="n">
         <v>580.89</v>
@@ -6547,10 +6547,10 @@
         <v>1.985348</v>
       </c>
       <c r="P94" t="n">
-        <v>1.985347985347985e-06</v>
+        <v>7.35314069e-05</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.985348</v>
+        <v>73.5314074</v>
       </c>
       <c r="R94" t="n">
         <v>577.9400000000001</v>
@@ -6612,10 +6612,10 @@
         <v>2.371998</v>
       </c>
       <c r="P95" t="n">
-        <v>2.371998371998372e-06</v>
+        <v>8.78517916e-05</v>
       </c>
       <c r="Q95" t="n">
-        <v>2.371998</v>
+        <v>87.8517778</v>
       </c>
       <c r="R95" t="n">
         <v>512.6</v>
@@ -6677,10 +6677,10 @@
         <v>2.328449</v>
       </c>
       <c r="P96" t="n">
-        <v>2.328449328449329e-06</v>
+        <v>8.6238864e-05</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.328449</v>
+        <v>86.2388519</v>
       </c>
       <c r="R96" t="n">
         <v>576.73</v>
@@ -6742,10 +6742,10 @@
         <v>2.281237</v>
       </c>
       <c r="P97" t="n">
-        <v>2.281237281237281e-06</v>
+        <v>8.44902697e-05</v>
       </c>
       <c r="Q97" t="n">
-        <v>2.281237</v>
+        <v>84.4902593</v>
       </c>
       <c r="R97" t="n">
         <v>516.11</v>
@@ -6807,10 +6807,10 @@
         <v>2.229955</v>
       </c>
       <c r="P98" t="n">
-        <v>2.22995522995523e-06</v>
+        <v>8.25909344e-05</v>
       </c>
       <c r="Q98" t="n">
-        <v>2.229955</v>
+        <v>82.5909259</v>
       </c>
       <c r="R98" t="n">
         <v>521.05</v>
@@ -6872,10 +6872,10 @@
         <v>2.188034</v>
       </c>
       <c r="P99" t="n">
-        <v>2.188034188034188e-06</v>
+        <v>8.10383033e-05</v>
       </c>
       <c r="Q99" t="n">
-        <v>2.188034</v>
+        <v>81.0382963</v>
       </c>
       <c r="R99" t="n">
         <v>571.76</v>
@@ -6937,10 +6937,10 @@
         <v>2.145706</v>
       </c>
       <c r="P100" t="n">
-        <v>2.145706145706145e-06</v>
+        <v>7.9470598e-05</v>
       </c>
       <c r="Q100" t="n">
-        <v>2.145706</v>
+        <v>79.4705926</v>
       </c>
       <c r="R100" t="n">
         <v>396.93</v>
@@ -7002,10 +7002,10 @@
         <v>2.098494</v>
       </c>
       <c r="P101" t="n">
-        <v>2.098494098494099e-06</v>
+        <v>7.77220036e-05</v>
       </c>
       <c r="Q101" t="n">
-        <v>2.098494</v>
+        <v>77.722</v>
       </c>
       <c r="R101" t="n">
         <v>406.22</v>
@@ -7067,10 +7067,10 @@
         <v>2.051282</v>
       </c>
       <c r="P102" t="n">
-        <v>2.051282051282051e-06</v>
+        <v>7.59734093e-05</v>
       </c>
       <c r="Q102" t="n">
-        <v>2.051282</v>
+        <v>75.9734074</v>
       </c>
       <c r="R102" t="n">
         <v>405.69</v>
@@ -7132,10 +7132,10 @@
         <v>2.012617</v>
       </c>
       <c r="P103" t="n">
-        <v>2.012617012617013e-06</v>
+        <v>7.45413708e-05</v>
       </c>
       <c r="Q103" t="n">
-        <v>2.012617</v>
+        <v>74.5413704</v>
       </c>
       <c r="R103" t="n">
         <v>407.89</v>
@@ -7197,10 +7197,10 @@
         <v>1.97151</v>
       </c>
       <c r="P104" t="n">
-        <v>1.971509971509971e-06</v>
+        <v>7.30188878e-05</v>
       </c>
       <c r="Q104" t="n">
-        <v>1.97151</v>
+        <v>73.0188889</v>
       </c>
       <c r="R104" t="n">
         <v>524.73</v>
@@ -7262,10 +7262,10 @@
         <v>1.935287</v>
       </c>
       <c r="P105" t="n">
-        <v>1.935286935286935e-06</v>
+        <v>7.16772939e-05</v>
       </c>
       <c r="Q105" t="n">
-        <v>1.935287</v>
+        <v>71.6772963</v>
       </c>
       <c r="R105" t="n">
         <v>511.85</v>
@@ -7327,10 +7327,10 @@
         <v>1.90232</v>
       </c>
       <c r="P106" t="n">
-        <v>1.902319902319902e-06</v>
+        <v>7.04562927e-05</v>
       </c>
       <c r="Q106" t="n">
-        <v>1.90232</v>
+        <v>70.4562963</v>
       </c>
       <c r="R106" t="n">
         <v>454</v>
@@ -7392,10 +7392,10 @@
         <v>1.86976</v>
       </c>
       <c r="P107" t="n">
-        <v>1.86975986975987e-06</v>
+        <v>6.92503655e-05</v>
       </c>
       <c r="Q107" t="n">
-        <v>1.86976</v>
+        <v>69.2503704</v>
       </c>
       <c r="R107" t="n">
         <v>394.05</v>
@@ -7457,10 +7457,10 @@
         <v>1.836793</v>
       </c>
       <c r="P108" t="n">
-        <v>1.836792836792837e-06</v>
+        <v>6.80293643e-05</v>
       </c>
       <c r="Q108" t="n">
-        <v>1.836793</v>
+        <v>68.0293704</v>
       </c>
       <c r="R108" t="n">
         <v>401.93</v>
@@ -7522,10 +7522,10 @@
         <v>1.805454</v>
       </c>
       <c r="P109" t="n">
-        <v>1.805453805453806e-06</v>
+        <v>6.68686595e-05</v>
       </c>
       <c r="Q109" t="n">
-        <v>1.805454</v>
+        <v>66.8686667</v>
       </c>
       <c r="R109" t="n">
         <v>524.41</v>
@@ -7587,10 +7587,10 @@
         <v>1.776964</v>
       </c>
       <c r="P110" t="n">
-        <v>1.776963776963777e-06</v>
+        <v>6.58134732e-05</v>
       </c>
       <c r="Q110" t="n">
-        <v>1.776964</v>
+        <v>65.8134815</v>
       </c>
       <c r="R110" t="n">
         <v>457.61</v>
@@ -7652,10 +7652,10 @@
         <v>1.753358</v>
       </c>
       <c r="P111" t="n">
-        <v>1.753357753357753e-06</v>
+        <v>6.49391761e-05</v>
       </c>
       <c r="Q111" t="n">
-        <v>1.753358</v>
+        <v>64.9391852</v>
       </c>
       <c r="R111" t="n">
         <v>514.09</v>
@@ -7717,10 +7717,10 @@
         <v>1.735857</v>
       </c>
       <c r="P112" t="n">
-        <v>1.735856735856736e-06</v>
+        <v>6.42909902e-05</v>
       </c>
       <c r="Q112" t="n">
-        <v>1.735857</v>
+        <v>64.291</v>
       </c>
       <c r="R112" t="n">
         <v>579.17</v>
@@ -7782,10 +7782,10 @@
         <v>1.7151</v>
       </c>
       <c r="P113" t="n">
-        <v>1.715099715099715e-06</v>
+        <v>6.35222117e-05</v>
       </c>
       <c r="Q113" t="n">
-        <v>1.7151</v>
+        <v>63.5222222</v>
       </c>
       <c r="R113" t="n">
         <v>579.72</v>
@@ -7847,10 +7847,10 @@
         <v>1.700041</v>
       </c>
       <c r="P114" t="n">
-        <v>1.7000407000407e-06</v>
+        <v>6.29644704e-05</v>
       </c>
       <c r="Q114" t="n">
-        <v>1.700041</v>
+        <v>62.9644815</v>
       </c>
       <c r="R114" t="n">
         <v>452.93</v>
@@ -7912,10 +7912,10 @@
         <v>1.689459</v>
       </c>
       <c r="P115" t="n">
-        <v>1.68945868945869e-06</v>
+        <v>6.25725441e-05</v>
       </c>
       <c r="Q115" t="n">
-        <v>1.689459</v>
+        <v>62.5725556</v>
       </c>
       <c r="R115" t="n">
         <v>512.25</v>
@@ -7977,10 +7977,10 @@
         <v>1.682133</v>
       </c>
       <c r="P116" t="n">
-        <v>1.682132682132682e-06</v>
+        <v>6.23012104e-05</v>
       </c>
       <c r="Q116" t="n">
-        <v>1.682133</v>
+        <v>62.3012222</v>
       </c>
       <c r="R116" t="n">
         <v>457.08</v>
@@ -8042,10 +8042,10 @@
         <v>1.682133</v>
       </c>
       <c r="P117" t="n">
-        <v>1.682132682132682e-06</v>
+        <v>6.23012104e-05</v>
       </c>
       <c r="Q117" t="n">
-        <v>1.682133</v>
+        <v>62.3012222</v>
       </c>
       <c r="R117" t="n">
         <v>511.76</v>
@@ -8107,10 +8107,10 @@
         <v>1.680098</v>
       </c>
       <c r="P118" t="n">
-        <v>1.68009768009768e-06</v>
+        <v>6.222584e-05</v>
       </c>
       <c r="Q118" t="n">
-        <v>1.680098</v>
+        <v>62.2258519</v>
       </c>
       <c r="R118" t="n">
         <v>516.92</v>
@@ -8172,10 +8172,10 @@
         <v>1.688238</v>
       </c>
       <c r="P119" t="n">
-        <v>1.688237688237688e-06</v>
+        <v>6.25273218e-05</v>
       </c>
       <c r="Q119" t="n">
-        <v>1.688238</v>
+        <v>62.5273333</v>
       </c>
       <c r="R119" t="n">
         <v>511.9</v>
@@ -8237,10 +8237,10 @@
         <v>1.698413</v>
       </c>
       <c r="P120" t="n">
-        <v>1.698412698412698e-06</v>
+        <v>6.2904174e-05</v>
       </c>
       <c r="Q120" t="n">
-        <v>1.698413</v>
+        <v>62.9041852</v>
       </c>
       <c r="R120" t="n">
         <v>575.04</v>
@@ -8302,10 +8302,10 @@
         <v>1.710216</v>
       </c>
       <c r="P121" t="n">
-        <v>1.71021571021571e-06</v>
+        <v>6.33413226e-05</v>
       </c>
       <c r="Q121" t="n">
-        <v>1.710216</v>
+        <v>63.3413333</v>
       </c>
       <c r="R121" t="n">
         <v>516.08</v>
@@ -8367,10 +8367,10 @@
         <v>1.723647</v>
       </c>
       <c r="P122" t="n">
-        <v>1.723646723646724e-06</v>
+        <v>6.38387675e-05</v>
       </c>
       <c r="Q122" t="n">
-        <v>1.723647</v>
+        <v>63.8387778</v>
       </c>
       <c r="R122" t="n">
         <v>514.91</v>
@@ -8432,10 +8432,10 @@
         <v>1.741962</v>
       </c>
       <c r="P123" t="n">
-        <v>1.741961741961742e-06</v>
+        <v>6.45171016e-05</v>
       </c>
       <c r="Q123" t="n">
-        <v>1.741962</v>
+        <v>64.5171111</v>
       </c>
       <c r="R123" t="n">
         <v>453.37</v>
@@ -8497,10 +8497,10 @@
         <v>1.769231</v>
       </c>
       <c r="P124" t="n">
-        <v>1.769230769230769e-06</v>
+        <v>6.55270655e-05</v>
       </c>
       <c r="Q124" t="n">
-        <v>1.769231</v>
+        <v>65.5270741</v>
       </c>
       <c r="R124" t="n">
         <v>514.85</v>
@@ -8562,10 +8562,10 @@
         <v>1.795686</v>
       </c>
       <c r="P125" t="n">
-        <v>1.795685795685796e-06</v>
+        <v>6.65068813e-05</v>
       </c>
       <c r="Q125" t="n">
-        <v>1.795686</v>
+        <v>66.5068889</v>
       </c>
       <c r="R125" t="n">
         <v>575.5</v>
@@ -8627,10 +8627,10 @@
         <v>2.125356</v>
       </c>
       <c r="P126" t="n">
-        <v>2.125356125356126e-06</v>
+        <v>7.87168935e-05</v>
       </c>
       <c r="Q126" t="n">
-        <v>2.125356</v>
+        <v>78.7168889</v>
       </c>
       <c r="R126" t="n">
         <v>509.82</v>
@@ -8692,10 +8692,10 @@
         <v>2.078958</v>
       </c>
       <c r="P127" t="n">
-        <v>2.078958078958079e-06</v>
+        <v>7.69984474e-05</v>
       </c>
       <c r="Q127" t="n">
-        <v>2.078958</v>
+        <v>76.9984444</v>
       </c>
       <c r="R127" t="n">
         <v>456.99</v>
@@ -8757,10 +8757,10 @@
         <v>2.029304</v>
       </c>
       <c r="P128" t="n">
-        <v>2.029304029304029e-06</v>
+        <v>7.51594085e-05</v>
       </c>
       <c r="Q128" t="n">
-        <v>2.029304</v>
+        <v>75.1594074</v>
       </c>
       <c r="R128" t="n">
         <v>509.65</v>
@@ -8822,10 +8822,10 @@
         <v>1.973138</v>
       </c>
       <c r="P129" t="n">
-        <v>1.973137973137973e-06</v>
+        <v>7.30791842e-05</v>
       </c>
       <c r="Q129" t="n">
-        <v>1.973138</v>
+        <v>73.0791852</v>
       </c>
       <c r="R129" t="n">
         <v>581.55</v>
@@ -8887,10 +8887,10 @@
         <v>1.919414</v>
       </c>
       <c r="P130" t="n">
-        <v>1.91941391941392e-06</v>
+        <v>7.10894044e-05</v>
       </c>
       <c r="Q130" t="n">
-        <v>1.919414</v>
+        <v>71.0894074</v>
       </c>
       <c r="R130" t="n">
         <v>512.52</v>
@@ -8952,10 +8952,10 @@
         <v>1.87383</v>
       </c>
       <c r="P131" t="n">
-        <v>1.873829873829874e-06</v>
+        <v>6.94011064e-05</v>
       </c>
       <c r="Q131" t="n">
-        <v>1.87383</v>
+        <v>69.4011111</v>
       </c>
       <c r="R131" t="n">
         <v>517.23</v>
@@ -9017,10 +9017,10 @@
         <v>1.829467</v>
       </c>
       <c r="P132" t="n">
-        <v>1.82946682946683e-06</v>
+        <v>6.77580307e-05</v>
       </c>
       <c r="Q132" t="n">
-        <v>1.829467</v>
+        <v>67.758037</v>
       </c>
       <c r="R132" t="n">
         <v>515.02</v>
@@ -9082,10 +9082,10 @@
         <v>1.778592</v>
       </c>
       <c r="P133" t="n">
-        <v>1.778591778591779e-06</v>
+        <v>6.58737696e-05</v>
       </c>
       <c r="Q133" t="n">
-        <v>1.778592</v>
+        <v>65.8737778</v>
       </c>
       <c r="R133" t="n">
         <v>455.22</v>
@@ -9147,10 +9147,10 @@
         <v>1.733415</v>
       </c>
       <c r="P134" t="n">
-        <v>1.733414733414733e-06</v>
+        <v>6.42005457e-05</v>
       </c>
       <c r="Q134" t="n">
-        <v>1.733415</v>
+        <v>64.2005556</v>
       </c>
       <c r="R134" t="n">
         <v>450.84</v>
@@ -9212,10 +9212,10 @@
         <v>1.693122</v>
       </c>
       <c r="P135" t="n">
-        <v>1.693121693121693e-06</v>
+        <v>6.27082109e-05</v>
       </c>
       <c r="Q135" t="n">
-        <v>1.693122</v>
+        <v>62.7082222</v>
       </c>
       <c r="R135" t="n">
         <v>579.97</v>
@@ -9277,10 +9277,10 @@
         <v>1.655678</v>
       </c>
       <c r="P136" t="n">
-        <v>1.655677655677656e-06</v>
+        <v>6.13213947e-05</v>
       </c>
       <c r="Q136" t="n">
-        <v>1.655678</v>
+        <v>61.3214074</v>
       </c>
       <c r="R136" t="n">
         <v>513.98</v>
@@ -9342,10 +9342,10 @@
         <v>1.621897</v>
       </c>
       <c r="P137" t="n">
-        <v>1.621896621896622e-06</v>
+        <v>6.00702453e-05</v>
       </c>
       <c r="Q137" t="n">
-        <v>1.621897</v>
+        <v>60.0702593</v>
       </c>
       <c r="R137" t="n">
         <v>453.92</v>
@@ -9407,10 +9407,10 @@
         <v>1.582011</v>
       </c>
       <c r="P138" t="n">
-        <v>1.582010582010582e-06</v>
+        <v>5.85929845e-05</v>
       </c>
       <c r="Q138" t="n">
-        <v>1.582011</v>
+        <v>58.593</v>
       </c>
       <c r="R138" t="n">
         <v>511.95</v>
@@ -9472,10 +9472,10 @@
         <v>1.558812</v>
       </c>
       <c r="P139" t="n">
-        <v>1.558811558811559e-06</v>
+        <v>5.77337614e-05</v>
       </c>
       <c r="Q139" t="n">
-        <v>1.558812</v>
+        <v>57.7337778</v>
       </c>
       <c r="R139" t="n">
         <v>515.16</v>
@@ -9537,10 +9537,10 @@
         <v>1.527066</v>
       </c>
       <c r="P140" t="n">
-        <v>1.527065527065527e-06</v>
+        <v>5.65579825e-05</v>
       </c>
       <c r="Q140" t="n">
-        <v>1.527066</v>
+        <v>56.558</v>
       </c>
       <c r="R140" t="n">
         <v>512.28</v>
@@ -9602,10 +9602,10 @@
         <v>1.50753</v>
       </c>
       <c r="P141" t="n">
-        <v>1.507529507529508e-06</v>
+        <v>5.58344262e-05</v>
       </c>
       <c r="Q141" t="n">
-        <v>1.50753</v>
+        <v>55.8344444</v>
       </c>
       <c r="R141" t="n">
         <v>455.34</v>
@@ -9667,10 +9667,10 @@
         <v>1.487993</v>
       </c>
       <c r="P142" t="n">
-        <v>1.487993487993488e-06</v>
+        <v>5.51108699e-05</v>
       </c>
       <c r="Q142" t="n">
-        <v>1.487993</v>
+        <v>55.1108519</v>
       </c>
       <c r="R142" t="n">
         <v>576.63</v>
@@ -9732,10 +9732,10 @@
         <v>1.47212</v>
       </c>
       <c r="P143" t="n">
-        <v>1.472120472120472e-06</v>
+        <v>5.45229804e-05</v>
       </c>
       <c r="Q143" t="n">
-        <v>1.47212</v>
+        <v>54.522963</v>
       </c>
       <c r="R143" t="n">
         <v>514.71</v>
@@ -9797,10 +9797,10 @@
         <v>1.46398</v>
       </c>
       <c r="P144" t="n">
-        <v>1.463980463980464e-06</v>
+        <v>5.42214987e-05</v>
       </c>
       <c r="Q144" t="n">
-        <v>1.46398</v>
+        <v>54.2214815</v>
       </c>
       <c r="R144" t="n">
         <v>523.3200000000001</v>
@@ -9862,10 +9862,10 @@
         <v>1.456654</v>
       </c>
       <c r="P145" t="n">
-        <v>1.456654456654457e-06</v>
+        <v>5.39501651e-05</v>
       </c>
       <c r="Q145" t="n">
-        <v>1.456654</v>
+        <v>53.9501481</v>
       </c>
       <c r="R145" t="n">
         <v>516.75</v>
@@ -9927,10 +9927,10 @@
         <v>1.451363</v>
       </c>
       <c r="P146" t="n">
-        <v>1.451363451363452e-06</v>
+        <v>5.37542019e-05</v>
       </c>
       <c r="Q146" t="n">
-        <v>1.451363</v>
+        <v>53.7541852</v>
       </c>
       <c r="R146" t="n">
         <v>577.08</v>
@@ -9992,10 +9992,10 @@
         <v>1.45177</v>
       </c>
       <c r="P147" t="n">
-        <v>1.451770451770452e-06</v>
+        <v>5.3769276e-05</v>
       </c>
       <c r="Q147" t="n">
-        <v>1.45177</v>
+        <v>53.7692593</v>
       </c>
       <c r="R147" t="n">
         <v>575.85</v>
@@ -10057,10 +10057,10 @@
         <v>1.461945</v>
       </c>
       <c r="P148" t="n">
-        <v>1.461945461945462e-06</v>
+        <v>5.41461282e-05</v>
       </c>
       <c r="Q148" t="n">
-        <v>1.461945</v>
+        <v>54.1461111</v>
       </c>
       <c r="R148" t="n">
         <v>455.21</v>
@@ -10122,10 +10122,10 @@
         <v>1.472934</v>
       </c>
       <c r="P149" t="n">
-        <v>1.472934472934473e-06</v>
+        <v>5.45531286e-05</v>
       </c>
       <c r="Q149" t="n">
-        <v>1.472934</v>
+        <v>54.5531111</v>
       </c>
       <c r="R149" t="n">
         <v>521.25</v>
@@ -10187,10 +10187,10 @@
         <v>1.487993</v>
       </c>
       <c r="P150" t="n">
-        <v>1.487993487993488e-06</v>
+        <v>5.51108699e-05</v>
       </c>
       <c r="Q150" t="n">
-        <v>1.487993</v>
+        <v>55.1108519</v>
       </c>
       <c r="R150" t="n">
         <v>514.54</v>
@@ -10252,10 +10252,10 @@
         <v>1.505495</v>
       </c>
       <c r="P151" t="n">
-        <v>1.505494505494506e-06</v>
+        <v>5.57590558e-05</v>
       </c>
       <c r="Q151" t="n">
-        <v>1.505495</v>
+        <v>55.7590741</v>
       </c>
       <c r="R151" t="n">
         <v>514.29</v>
@@ -10317,10 +10317,10 @@
         <v>1.529508</v>
       </c>
       <c r="P152" t="n">
-        <v>1.529507529507529e-06</v>
+        <v>5.6648427e-05</v>
       </c>
       <c r="Q152" t="n">
-        <v>1.529508</v>
+        <v>56.6484444</v>
       </c>
       <c r="R152" t="n">
         <v>575.72</v>
@@ -10382,10 +10382,10 @@
         <v>1.5523</v>
       </c>
       <c r="P153" t="n">
-        <v>1.552299552299552e-06</v>
+        <v>5.7492576e-05</v>
       </c>
       <c r="Q153" t="n">
-        <v>1.5523</v>
+        <v>57.4925926</v>
       </c>
       <c r="R153" t="n">
         <v>579.9299999999999</v>
@@ -10447,10 +10447,10 @@
         <v>1.577534</v>
       </c>
       <c r="P154" t="n">
-        <v>1.577533577533577e-06</v>
+        <v>5.84271695e-05</v>
       </c>
       <c r="Q154" t="n">
-        <v>1.577534</v>
+        <v>58.4271852</v>
       </c>
       <c r="R154" t="n">
         <v>573.97</v>
@@ -10512,10 +10512,10 @@
         <v>1.619048</v>
       </c>
       <c r="P155" t="n">
-        <v>1.619047619047619e-06</v>
+        <v>5.99647266e-05</v>
       </c>
       <c r="Q155" t="n">
-        <v>1.619048</v>
+        <v>59.9647407</v>
       </c>
       <c r="R155" t="n">
         <v>512.1900000000001</v>
@@ -10577,10 +10577,10 @@
         <v>1.656085</v>
       </c>
       <c r="P156" t="n">
-        <v>1.656084656084656e-06</v>
+        <v>6.13364687e-05</v>
       </c>
       <c r="Q156" t="n">
-        <v>1.656085</v>
+        <v>61.3364815</v>
       </c>
       <c r="R156" t="n">
         <v>457.33</v>
@@ -10642,10 +10642,10 @@
         <v>1.86569</v>
       </c>
       <c r="P157" t="n">
-        <v>1.865689865689866e-06</v>
+        <v>6.90996247e-05</v>
       </c>
       <c r="Q157" t="n">
-        <v>1.86569</v>
+        <v>69.0996296</v>
       </c>
       <c r="R157" t="n">
         <v>516.98</v>
@@ -10707,10 +10707,10 @@
         <v>1.808303</v>
       </c>
       <c r="P158" t="n">
-        <v>1.808302808302808e-06</v>
+        <v>6.69741781e-05</v>
       </c>
       <c r="Q158" t="n">
-        <v>1.808303</v>
+        <v>66.9741852</v>
       </c>
       <c r="R158" t="n">
         <v>514.9400000000001</v>
@@ -10772,10 +10772,10 @@
         <v>1.754579</v>
       </c>
       <c r="P159" t="n">
-        <v>1.754578754578755e-06</v>
+        <v>6.49843983e-05</v>
       </c>
       <c r="Q159" t="n">
-        <v>1.754579</v>
+        <v>64.9844074</v>
       </c>
       <c r="R159" t="n">
         <v>582.16</v>
@@ -10837,10 +10837,10 @@
         <v>1.701669</v>
       </c>
       <c r="P160" t="n">
-        <v>1.701668701668702e-06</v>
+        <v>6.30247667e-05</v>
       </c>
       <c r="Q160" t="n">
-        <v>1.701669</v>
+        <v>63.0247778</v>
       </c>
       <c r="R160" t="n">
         <v>456.15</v>
@@ -10902,10 +10902,10 @@
         <v>1.646317</v>
       </c>
       <c r="P161" t="n">
-        <v>1.646316646316646e-06</v>
+        <v>6.09746906e-05</v>
       </c>
       <c r="Q161" t="n">
-        <v>1.646317</v>
+        <v>60.9747037</v>
       </c>
       <c r="R161" t="n">
         <v>395</v>
@@ -10967,10 +10967,10 @@
         <v>1.596256</v>
       </c>
       <c r="P162" t="n">
-        <v>1.596255596255596e-06</v>
+        <v>5.91205776e-05</v>
       </c>
       <c r="Q162" t="n">
-        <v>1.596256</v>
+        <v>59.1205926</v>
       </c>
       <c r="R162" t="n">
         <v>528.26</v>
@@ -11032,10 +11032,10 @@
         <v>1.554742</v>
       </c>
       <c r="P163" t="n">
-        <v>1.554741554741555e-06</v>
+        <v>5.75830205e-05</v>
       </c>
       <c r="Q163" t="n">
-        <v>1.554742</v>
+        <v>57.583037</v>
       </c>
       <c r="R163" t="n">
         <v>513.6799999999999</v>
@@ -11097,10 +11097,10 @@
         <v>1.509972</v>
       </c>
       <c r="P164" t="n">
-        <v>1.50997150997151e-06</v>
+        <v>5.59248707e-05</v>
       </c>
       <c r="Q164" t="n">
-        <v>1.509972</v>
+        <v>55.9248889</v>
       </c>
       <c r="R164" t="n">
         <v>511.88</v>
@@ -11162,10 +11162,10 @@
         <v>1.464387</v>
       </c>
       <c r="P165" t="n">
-        <v>1.464387464387464e-06</v>
+        <v>5.42365728e-05</v>
       </c>
       <c r="Q165" t="n">
-        <v>1.464387</v>
+        <v>54.2365556</v>
       </c>
       <c r="R165" t="n">
         <v>459.12</v>
@@ -11227,10 +11227,10 @@
         <v>1.426129</v>
       </c>
       <c r="P166" t="n">
-        <v>1.426129426129426e-06</v>
+        <v>5.28196084e-05</v>
       </c>
       <c r="Q166" t="n">
-        <v>1.426129</v>
+        <v>52.8195926</v>
       </c>
       <c r="R166" t="n">
         <v>521</v>
@@ -11292,10 +11292,10 @@
         <v>1.391127</v>
       </c>
       <c r="P167" t="n">
-        <v>1.391127391127391e-06</v>
+        <v>5.15232367e-05</v>
       </c>
       <c r="Q167" t="n">
-        <v>1.391127</v>
+        <v>51.5232222</v>
       </c>
       <c r="R167" t="n">
         <v>455.54</v>
@@ -11357,10 +11357,10 @@
         <v>1.360602</v>
       </c>
       <c r="P168" t="n">
-        <v>1.360602360602361e-06</v>
+        <v>5.039268e-05</v>
       </c>
       <c r="Q168" t="n">
-        <v>1.360602</v>
+        <v>50.3926667</v>
       </c>
       <c r="R168" t="n">
         <v>585.71</v>
@@ -11422,10 +11422,10 @@
         <v>1.332519</v>
       </c>
       <c r="P169" t="n">
-        <v>1.332519332519333e-06</v>
+        <v>4.93525679e-05</v>
       </c>
       <c r="Q169" t="n">
-        <v>1.332519</v>
+        <v>49.3525556</v>
       </c>
       <c r="R169" t="n">
         <v>512.75</v>
@@ -11487,10 +11487,10 @@
         <v>1.306471</v>
       </c>
       <c r="P170" t="n">
-        <v>1.306471306471306e-06</v>
+        <v>4.83878262e-05</v>
       </c>
       <c r="Q170" t="n">
-        <v>1.306471</v>
+        <v>48.3878148</v>
       </c>
       <c r="R170" t="n">
         <v>577.11</v>
@@ -11552,10 +11552,10 @@
         <v>1.289784</v>
       </c>
       <c r="P171" t="n">
-        <v>1.28978428978429e-06</v>
+        <v>4.77697885e-05</v>
       </c>
       <c r="Q171" t="n">
-        <v>1.289784</v>
+        <v>47.7697778</v>
       </c>
       <c r="R171" t="n">
         <v>450.99</v>
@@ -11617,10 +11617,10 @@
         <v>1.272283</v>
       </c>
       <c r="P172" t="n">
-        <v>1.272283272283272e-06</v>
+        <v>4.71216027e-05</v>
       </c>
       <c r="Q172" t="n">
-        <v>1.272283</v>
+        <v>47.1215926</v>
       </c>
       <c r="R172" t="n">
         <v>516.8</v>
@@ -11682,10 +11682,10 @@
         <v>1.265364</v>
       </c>
       <c r="P173" t="n">
-        <v>1.265364265364265e-06</v>
+        <v>4.68653432e-05</v>
       </c>
       <c r="Q173" t="n">
-        <v>1.265364</v>
+        <v>46.8653333</v>
       </c>
       <c r="R173" t="n">
         <v>575.1</v>
@@ -11747,10 +11747,10 @@
         <v>1.25641</v>
       </c>
       <c r="P174" t="n">
-        <v>1.256410256410256e-06</v>
+        <v>4.65337132e-05</v>
       </c>
       <c r="Q174" t="n">
-        <v>1.25641</v>
+        <v>46.5337037</v>
       </c>
       <c r="R174" t="n">
         <v>517.55</v>
@@ -11812,10 +11812,10 @@
         <v>1.262922</v>
       </c>
       <c r="P175" t="n">
-        <v>1.262922262922263e-06</v>
+        <v>4.67748986e-05</v>
       </c>
       <c r="Q175" t="n">
-        <v>1.262922</v>
+        <v>46.7748889</v>
       </c>
       <c r="R175" t="n">
         <v>514.9</v>
@@ -11877,10 +11877,10 @@
         <v>1.262108</v>
       </c>
       <c r="P176" t="n">
-        <v>1.262108262108262e-06</v>
+        <v>4.67447504e-05</v>
       </c>
       <c r="Q176" t="n">
-        <v>1.262108</v>
+        <v>46.7447407</v>
       </c>
       <c r="R176" t="n">
         <v>455.23</v>
@@ -11942,10 +11942,10 @@
         <v>1.273911</v>
       </c>
       <c r="P177" t="n">
-        <v>1.273911273911274e-06</v>
+        <v>4.7181899e-05</v>
       </c>
       <c r="Q177" t="n">
-        <v>1.273911</v>
+        <v>47.1818889</v>
       </c>
       <c r="R177" t="n">
         <v>529.17</v>
@@ -12007,10 +12007,10 @@
         <v>1.286121</v>
       </c>
       <c r="P178" t="n">
-        <v>1.286121286121286e-06</v>
+        <v>4.76341217e-05</v>
       </c>
       <c r="Q178" t="n">
-        <v>1.286121</v>
+        <v>47.6341111</v>
       </c>
       <c r="R178" t="n">
         <v>510.58</v>
@@ -12072,10 +12072,10 @@
         <v>1.304029</v>
       </c>
       <c r="P179" t="n">
-        <v>1.304029304029304e-06</v>
+        <v>4.82973816e-05</v>
       </c>
       <c r="Q179" t="n">
-        <v>1.304029</v>
+        <v>48.2973704</v>
       </c>
       <c r="R179" t="n">
         <v>457.64</v>
@@ -12137,10 +12137,10 @@
         <v>1.332519</v>
       </c>
       <c r="P180" t="n">
-        <v>1.332519332519333e-06</v>
+        <v>4.93525679e-05</v>
       </c>
       <c r="Q180" t="n">
-        <v>1.332519</v>
+        <v>49.3525556</v>
       </c>
       <c r="R180" t="n">
         <v>573.8099999999999</v>
@@ -12202,10 +12202,10 @@
         <v>1.346357</v>
       </c>
       <c r="P181" t="n">
-        <v>1.346357346357346e-06</v>
+        <v>4.98650869e-05</v>
       </c>
       <c r="Q181" t="n">
-        <v>1.346357</v>
+        <v>49.8650741</v>
       </c>
       <c r="R181" t="n">
         <v>515</v>
@@ -12267,10 +12267,10 @@
         <v>1.379731</v>
       </c>
       <c r="P182" t="n">
-        <v>1.37973137973138e-06</v>
+        <v>5.11011622e-05</v>
       </c>
       <c r="Q182" t="n">
-        <v>1.379731</v>
+        <v>51.1011481</v>
       </c>
       <c r="R182" t="n">
         <v>399.71</v>
@@ -12332,10 +12332,10 @@
         <v>1.408221</v>
       </c>
       <c r="P183" t="n">
-        <v>1.408221408221408e-06</v>
+        <v>5.21563485e-05</v>
       </c>
       <c r="Q183" t="n">
-        <v>1.408221</v>
+        <v>52.1563333</v>
       </c>
       <c r="R183" t="n">
         <v>467.06</v>
@@ -12397,10 +12397,10 @@
         <v>1.445258</v>
       </c>
       <c r="P184" t="n">
-        <v>1.445258445258445e-06</v>
+        <v>5.35280906e-05</v>
       </c>
       <c r="Q184" t="n">
-        <v>1.445258</v>
+        <v>53.5280741</v>
       </c>
       <c r="R184" t="n">
         <v>587.39</v>
@@ -12462,10 +12462,10 @@
         <v>1.490842</v>
       </c>
       <c r="P185" t="n">
-        <v>1.490842490842491e-06</v>
+        <v>5.52163885e-05</v>
       </c>
       <c r="Q185" t="n">
-        <v>1.490842</v>
+        <v>55.2163704</v>
       </c>
       <c r="R185" t="n">
         <v>397.29</v>
@@ -12527,10 +12527,10 @@
         <v>1.529915</v>
       </c>
       <c r="P186" t="n">
-        <v>1.52991452991453e-06</v>
+        <v>5.66635011e-05</v>
       </c>
       <c r="Q186" t="n">
-        <v>1.529915</v>
+        <v>56.6635185</v>
       </c>
       <c r="R186" t="n">
         <v>530.35</v>
@@ -12592,10 +12592,10 @@
         <v>1.579162</v>
       </c>
       <c r="P187" t="n">
-        <v>1.579161579161579e-06</v>
+        <v>5.84874659e-05</v>
       </c>
       <c r="Q187" t="n">
-        <v>1.579162</v>
+        <v>58.4874815</v>
       </c>
       <c r="R187" t="n">
         <v>511.84</v>
@@ -12657,10 +12657,10 @@
         <v>1.612536</v>
       </c>
       <c r="P188" t="n">
-        <v>1.612535612535613e-06</v>
+        <v>5.97235412e-05</v>
       </c>
       <c r="Q188" t="n">
-        <v>1.612536</v>
+        <v>59.7235556</v>
       </c>
       <c r="R188" t="n">
         <v>453.88</v>
@@ -12722,10 +12722,10 @@
         <v>1.566952</v>
       </c>
       <c r="P189" t="n">
-        <v>1.566951566951567e-06</v>
+        <v>5.80352432e-05</v>
       </c>
       <c r="Q189" t="n">
-        <v>1.566952</v>
+        <v>58.0352593</v>
       </c>
       <c r="R189" t="n">
         <v>390.74</v>
@@ -12787,10 +12787,10 @@
         <v>1.5116</v>
       </c>
       <c r="P190" t="n">
-        <v>1.511599511599512e-06</v>
+        <v>5.59851671e-05</v>
       </c>
       <c r="Q190" t="n">
-        <v>1.5116</v>
+        <v>55.9851852</v>
       </c>
       <c r="R190" t="n">
         <v>467.39</v>
@@ -12852,10 +12852,10 @@
         <v>1.461131</v>
       </c>
       <c r="P191" t="n">
-        <v>1.461131461131461e-06</v>
+        <v>5.411598e-05</v>
       </c>
       <c r="Q191" t="n">
-        <v>1.461131</v>
+        <v>54.115963</v>
       </c>
       <c r="R191" t="n">
         <v>508.15</v>
@@ -12917,10 +12917,10 @@
         <v>1.417989</v>
       </c>
       <c r="P192" t="n">
-        <v>1.417989417989418e-06</v>
+        <v>5.25181266e-05</v>
       </c>
       <c r="Q192" t="n">
-        <v>1.417989</v>
+        <v>52.5181111</v>
       </c>
       <c r="R192" t="n">
         <v>452.99</v>
@@ -12982,10 +12982,10 @@
         <v>1.372405</v>
       </c>
       <c r="P193" t="n">
-        <v>1.372405372405372e-06</v>
+        <v>5.08298286e-05</v>
       </c>
       <c r="Q193" t="n">
-        <v>1.372405</v>
+        <v>50.8298148</v>
       </c>
       <c r="R193" t="n">
         <v>516.5599999999999</v>
@@ -13047,10 +13047,10 @@
         <v>1.332112</v>
       </c>
       <c r="P194" t="n">
-        <v>1.332112332112332e-06</v>
+        <v>4.93374938e-05</v>
       </c>
       <c r="Q194" t="n">
-        <v>1.332112</v>
+        <v>49.3374815</v>
       </c>
       <c r="R194" t="n">
         <v>511.3</v>
@@ -13112,10 +13112,10 @@
         <v>1.29711</v>
       </c>
       <c r="P195" t="n">
-        <v>1.297110297110297e-06</v>
+        <v>4.80411221e-05</v>
       </c>
       <c r="Q195" t="n">
-        <v>1.29711</v>
+        <v>48.0411111</v>
       </c>
       <c r="R195" t="n">
         <v>451.01</v>
@@ -13177,10 +13177,10 @@
         <v>1.263329</v>
       </c>
       <c r="P196" t="n">
-        <v>1.263329263329264e-06</v>
+        <v>4.67899727e-05</v>
       </c>
       <c r="Q196" t="n">
-        <v>1.263329</v>
+        <v>46.789963</v>
       </c>
       <c r="R196" t="n">
         <v>394.95</v>
@@ -13242,10 +13242,10 @@
         <v>1.238502</v>
       </c>
       <c r="P197" t="n">
-        <v>1.238502238502239e-06</v>
+        <v>4.58704533e-05</v>
       </c>
       <c r="Q197" t="n">
-        <v>1.238502</v>
+        <v>45.8704444</v>
       </c>
       <c r="R197" t="n">
         <v>527.73</v>
@@ -13307,10 +13307,10 @@
         <v>1.217338</v>
       </c>
       <c r="P198" t="n">
-        <v>1.217338217338217e-06</v>
+        <v>4.50866006e-05</v>
       </c>
       <c r="Q198" t="n">
-        <v>1.217338</v>
+        <v>45.0865926</v>
       </c>
       <c r="R198" t="n">
         <v>508.99</v>
@@ -13372,10 +13372,10 @@
         <v>1.197802</v>
       </c>
       <c r="P199" t="n">
-        <v>1.197802197802198e-06</v>
+        <v>4.43630444e-05</v>
       </c>
       <c r="Q199" t="n">
-        <v>1.197802</v>
+        <v>44.363037</v>
       </c>
       <c r="R199" t="n">
         <v>453.68</v>
@@ -13437,10 +13437,10 @@
         <v>1.18315</v>
       </c>
       <c r="P200" t="n">
-        <v>1.183150183150183e-06</v>
+        <v>4.38203772e-05</v>
       </c>
       <c r="Q200" t="n">
-        <v>1.18315</v>
+        <v>43.8203704</v>
       </c>
       <c r="R200" t="n">
         <v>451.27</v>
@@ -13502,10 +13502,10 @@
         <v>1.17501</v>
       </c>
       <c r="P201" t="n">
-        <v>1.175010175010175e-06</v>
+        <v>4.35188954e-05</v>
       </c>
       <c r="Q201" t="n">
-        <v>1.17501</v>
+        <v>43.5188889</v>
       </c>
       <c r="R201" t="n">
         <v>455.82</v>
@@ -13567,10 +13567,10 @@
         <v>1.168905</v>
       </c>
       <c r="P202" t="n">
-        <v>1.168905168905169e-06</v>
+        <v>4.3292784e-05</v>
       </c>
       <c r="Q202" t="n">
-        <v>1.168905</v>
+        <v>43.2927778</v>
       </c>
       <c r="R202" t="n">
         <v>514.55</v>
@@ -13632,10 +13632,10 @@
         <v>1.171347</v>
       </c>
       <c r="P203" t="n">
-        <v>1.171347171347172e-06</v>
+        <v>4.33832286e-05</v>
       </c>
       <c r="Q203" t="n">
-        <v>1.171347</v>
+        <v>43.3832222</v>
       </c>
       <c r="R203" t="n">
         <v>517.61</v>
@@ -13697,10 +13697,10 @@
         <v>1.174603</v>
       </c>
       <c r="P204" t="n">
-        <v>1.174603174603175e-06</v>
+        <v>4.35038213e-05</v>
       </c>
       <c r="Q204" t="n">
-        <v>1.174603</v>
+        <v>43.5038148</v>
       </c>
       <c r="R204" t="n">
         <v>516.0599999999999</v>
@@ -13762,10 +13762,10 @@
         <v>1.181115</v>
       </c>
       <c r="P205" t="n">
-        <v>1.181115181115181e-06</v>
+        <v>4.37450067e-05</v>
       </c>
       <c r="Q205" t="n">
-        <v>1.181115</v>
+        <v>43.745</v>
       </c>
       <c r="R205" t="n">
         <v>579.76</v>
@@ -13827,10 +13827,10 @@
         <v>1.192918</v>
       </c>
       <c r="P206" t="n">
-        <v>1.192918192918193e-06</v>
+        <v>4.41821553e-05</v>
       </c>
       <c r="Q206" t="n">
-        <v>1.192918</v>
+        <v>44.1821481</v>
       </c>
       <c r="R206" t="n">
         <v>454.4</v>
@@ -13892,10 +13892,10 @@
         <v>1.21164</v>
       </c>
       <c r="P207" t="n">
-        <v>1.211640211640212e-06</v>
+        <v>4.48755634e-05</v>
       </c>
       <c r="Q207" t="n">
-        <v>1.21164</v>
+        <v>44.8755556</v>
       </c>
       <c r="R207" t="n">
         <v>589.39</v>
@@ -13957,10 +13957,10 @@
         <v>1.24013</v>
       </c>
       <c r="P208" t="n">
-        <v>1.24013024013024e-06</v>
+        <v>4.59307496e-05</v>
       </c>
       <c r="Q208" t="n">
-        <v>1.24013</v>
+        <v>45.9307407</v>
       </c>
       <c r="R208" t="n">
         <v>457.19</v>
@@ -14022,10 +14022,10 @@
         <v>1.263736</v>
       </c>
       <c r="P209" t="n">
-        <v>1.263736263736264e-06</v>
+        <v>4.68050468e-05</v>
       </c>
       <c r="Q209" t="n">
-        <v>1.263736</v>
+        <v>46.805037</v>
       </c>
       <c r="R209" t="n">
         <v>513.29</v>
@@ -14087,10 +14087,10 @@
         <v>1.294261</v>
       </c>
       <c r="P210" t="n">
-        <v>1.294261294261294e-06</v>
+        <v>4.79356035e-05</v>
       </c>
       <c r="Q210" t="n">
-        <v>1.294261</v>
+        <v>47.9355926</v>
       </c>
       <c r="R210" t="n">
         <v>516.74</v>
@@ -14152,10 +14152,10 @@
         <v>1.330891</v>
       </c>
       <c r="P211" t="n">
-        <v>1.330891330891331e-06</v>
+        <v>4.92922715e-05</v>
       </c>
       <c r="Q211" t="n">
-        <v>1.330891</v>
+        <v>49.2922593</v>
       </c>
       <c r="R211" t="n">
         <v>511.77</v>
@@ -14217,10 +14217,10 @@
         <v>1.367521</v>
       </c>
       <c r="P212" t="n">
-        <v>1.367521367521368e-06</v>
+        <v>5.06489395e-05</v>
       </c>
       <c r="Q212" t="n">
-        <v>1.367521</v>
+        <v>50.6489259</v>
       </c>
       <c r="R212" t="n">
         <v>517.5599999999999</v>
@@ -14282,10 +14282,10 @@
         <v>1.407814</v>
       </c>
       <c r="P213" t="n">
-        <v>1.407814407814408e-06</v>
+        <v>5.21412744e-05</v>
       </c>
       <c r="Q213" t="n">
-        <v>1.407814</v>
+        <v>52.1412593</v>
       </c>
       <c r="R213" t="n">
         <v>521.27</v>
@@ -14347,10 +14347,10 @@
         <v>1.461945</v>
       </c>
       <c r="P214" t="n">
-        <v>1.461945461945462e-06</v>
+        <v>5.41461282e-05</v>
       </c>
       <c r="Q214" t="n">
-        <v>1.461945</v>
+        <v>54.1461111</v>
       </c>
       <c r="R214" t="n">
         <v>510.97</v>
@@ -14412,10 +14412,10 @@
         <v>1.504274</v>
       </c>
       <c r="P215" t="n">
-        <v>1.504273504273504e-06</v>
+        <v>5.57138335e-05</v>
       </c>
       <c r="Q215" t="n">
-        <v>1.504274</v>
+        <v>55.7138519</v>
       </c>
       <c r="R215" t="n">
         <v>513.2</v>
@@ -14477,10 +14477,10 @@
         <v>1.559219</v>
       </c>
       <c r="P216" t="n">
-        <v>1.559218559218559e-06</v>
+        <v>5.77488355e-05</v>
       </c>
       <c r="Q216" t="n">
-        <v>1.559219</v>
+        <v>57.7488519</v>
       </c>
       <c r="R216" t="n">
         <v>514.75</v>
@@ -14542,10 +14542,10 @@
         <v>1.614978</v>
       </c>
       <c r="P217" t="n">
-        <v>1.614977614977615e-06</v>
+        <v>5.98139857e-05</v>
       </c>
       <c r="Q217" t="n">
-        <v>1.614978</v>
+        <v>59.814</v>
       </c>
       <c r="R217" t="n">
         <v>459.96</v>
@@ -14607,10 +14607,10 @@
         <v>1.673586</v>
       </c>
       <c r="P218" t="n">
-        <v>1.673585673585674e-06</v>
+        <v>6.19846546e-05</v>
       </c>
       <c r="Q218" t="n">
-        <v>1.673586</v>
+        <v>61.9846667</v>
       </c>
       <c r="R218" t="n">
         <v>466.21</v>
@@ -14672,10 +14672,10 @@
         <v>1.393569</v>
       </c>
       <c r="P219" t="n">
-        <v>1.393569393569394e-06</v>
+        <v>5.16136812e-05</v>
       </c>
       <c r="Q219" t="n">
-        <v>1.393569</v>
+        <v>51.6136667</v>
       </c>
       <c r="R219" t="n">
         <v>582.12</v>
@@ -14737,10 +14737,10 @@
         <v>1.355718</v>
       </c>
       <c r="P220" t="n">
-        <v>1.355718355718356e-06</v>
+        <v>5.0211791e-05</v>
       </c>
       <c r="Q220" t="n">
-        <v>1.355718</v>
+        <v>50.2117778</v>
       </c>
       <c r="R220" t="n">
         <v>449.75</v>
@@ -14802,10 +14802,10 @@
         <v>1.310948</v>
       </c>
       <c r="P221" t="n">
-        <v>1.310948310948311e-06</v>
+        <v>4.85536411e-05</v>
       </c>
       <c r="Q221" t="n">
-        <v>1.310948</v>
+        <v>48.5536296</v>
       </c>
       <c r="R221" t="n">
         <v>455.11</v>
@@ -14867,10 +14867,10 @@
         <v>1.275539</v>
       </c>
       <c r="P222" t="n">
-        <v>1.275539275539276e-06</v>
+        <v>4.72421954e-05</v>
       </c>
       <c r="Q222" t="n">
-        <v>1.275539</v>
+        <v>47.2421852</v>
       </c>
       <c r="R222" t="n">
         <v>520.03</v>
@@ -14932,10 +14932,10 @@
         <v>1.240537</v>
       </c>
       <c r="P223" t="n">
-        <v>1.240537240537241e-06</v>
+        <v>4.59458237e-05</v>
       </c>
       <c r="Q223" t="n">
-        <v>1.240537</v>
+        <v>45.9458148</v>
       </c>
       <c r="R223" t="n">
         <v>454.17</v>
@@ -14997,10 +14997,10 @@
         <v>1.21164</v>
       </c>
       <c r="P224" t="n">
-        <v>1.211640211640212e-06</v>
+        <v>4.48755634e-05</v>
       </c>
       <c r="Q224" t="n">
-        <v>1.21164</v>
+        <v>44.8755556</v>
       </c>
       <c r="R224" t="n">
         <v>395.64</v>
@@ -15062,10 +15062,10 @@
         <v>1.186813</v>
       </c>
       <c r="P225" t="n">
-        <v>1.186813186813187e-06</v>
+        <v>4.3956044e-05</v>
       </c>
       <c r="Q225" t="n">
-        <v>1.186813</v>
+        <v>43.956037</v>
       </c>
       <c r="R225" t="n">
         <v>527.24</v>
@@ -15127,10 +15127,10 @@
         <v>1.168905</v>
       </c>
       <c r="P226" t="n">
-        <v>1.168905168905169e-06</v>
+        <v>4.3292784e-05</v>
       </c>
       <c r="Q226" t="n">
-        <v>1.168905</v>
+        <v>43.2927778</v>
       </c>
       <c r="R226" t="n">
         <v>510.12</v>
@@ -15192,10 +15192,10 @@
         <v>1.150183</v>
       </c>
       <c r="P227" t="n">
-        <v>1.15018315018315e-06</v>
+        <v>4.25993759e-05</v>
       </c>
       <c r="Q227" t="n">
-        <v>1.150183</v>
+        <v>42.5993704</v>
       </c>
       <c r="R227" t="n">
         <v>518.59</v>
@@ -15257,10 +15257,10 @@
         <v>1.139194</v>
       </c>
       <c r="P228" t="n">
-        <v>1.139194139194139e-06</v>
+        <v>4.21923755e-05</v>
       </c>
       <c r="Q228" t="n">
-        <v>1.139194</v>
+        <v>42.1923704</v>
       </c>
       <c r="R228" t="n">
         <v>509.32</v>
@@ -15322,10 +15322,10 @@
         <v>1.133903</v>
       </c>
       <c r="P229" t="n">
-        <v>1.133903133903134e-06</v>
+        <v>4.19964124e-05</v>
       </c>
       <c r="Q229" t="n">
-        <v>1.133903</v>
+        <v>41.9964074</v>
       </c>
       <c r="R229" t="n">
         <v>516.41</v>
@@ -15387,10 +15387,10 @@
         <v>1.129019</v>
       </c>
       <c r="P230" t="n">
-        <v>1.129019129019129e-06</v>
+        <v>4.18155233e-05</v>
       </c>
       <c r="Q230" t="n">
-        <v>1.129019</v>
+        <v>41.8155185</v>
       </c>
       <c r="R230" t="n">
         <v>575.29</v>
@@ -15452,10 +15452,10 @@
         <v>1.135531</v>
       </c>
       <c r="P231" t="n">
-        <v>1.135531135531136e-06</v>
+        <v>4.20567087e-05</v>
       </c>
       <c r="Q231" t="n">
-        <v>1.135531</v>
+        <v>42.0567037</v>
       </c>
       <c r="R231" t="n">
         <v>513.45</v>
@@ -15517,10 +15517,10 @@
         <v>1.144078</v>
       </c>
       <c r="P232" t="n">
-        <v>1.144078144078144e-06</v>
+        <v>4.23732646e-05</v>
       </c>
       <c r="Q232" t="n">
-        <v>1.144078</v>
+        <v>42.3732593</v>
       </c>
       <c r="R232" t="n">
         <v>515.83</v>
@@ -15582,10 +15582,10 @@
         <v>1.153439</v>
       </c>
       <c r="P233" t="n">
-        <v>1.153439153439153e-06</v>
+        <v>4.27199686e-05</v>
       </c>
       <c r="Q233" t="n">
-        <v>1.153439</v>
+        <v>42.719963</v>
       </c>
       <c r="R233" t="n">
         <v>457.78</v>
@@ -15647,10 +15647,10 @@
         <v>1.173382</v>
       </c>
       <c r="P234" t="n">
-        <v>1.173382173382174e-06</v>
+        <v>4.3458599e-05</v>
       </c>
       <c r="Q234" t="n">
-        <v>1.173382</v>
+        <v>43.4585926</v>
       </c>
       <c r="R234" t="n">
         <v>462.03</v>
@@ -15712,10 +15712,10 @@
         <v>1.193732</v>
       </c>
       <c r="P235" t="n">
-        <v>1.193732193732194e-06</v>
+        <v>4.42123035e-05</v>
       </c>
       <c r="Q235" t="n">
-        <v>1.193732</v>
+        <v>44.2122963</v>
       </c>
       <c r="R235" t="n">
         <v>399</v>
@@ -15777,10 +15777,10 @@
         <v>1.221815</v>
       </c>
       <c r="P236" t="n">
-        <v>1.221815221815222e-06</v>
+        <v>4.52524156e-05</v>
       </c>
       <c r="Q236" t="n">
-        <v>1.221815</v>
+        <v>45.2524074</v>
       </c>
       <c r="R236" t="n">
         <v>580.22</v>
@@ -15842,10 +15842,10 @@
         <v>1.251119</v>
       </c>
       <c r="P237" t="n">
-        <v>1.251119251119251e-06</v>
+        <v>4.633775e-05</v>
       </c>
       <c r="Q237" t="n">
-        <v>1.251119</v>
+        <v>46.3377407</v>
       </c>
       <c r="R237" t="n">
         <v>574.84</v>
@@ -15907,10 +15907,10 @@
         <v>1.286528</v>
       </c>
       <c r="P238" t="n">
-        <v>1.286528286528287e-06</v>
+        <v>4.76491958e-05</v>
       </c>
       <c r="Q238" t="n">
-        <v>1.286528</v>
+        <v>47.6491852</v>
       </c>
       <c r="R238" t="n">
         <v>519.74</v>
@@ -15972,10 +15972,10 @@
         <v>1.326821</v>
       </c>
       <c r="P239" t="n">
-        <v>1.326821326821327e-06</v>
+        <v>4.91415306e-05</v>
       </c>
       <c r="Q239" t="n">
-        <v>1.326821</v>
+        <v>49.1415185</v>
       </c>
       <c r="R239" t="n">
         <v>510.22</v>
@@ -16037,10 +16037,10 @@
         <v>1.369556</v>
       </c>
       <c r="P240" t="n">
-        <v>1.36955636955637e-06</v>
+        <v>5.072431e-05</v>
       </c>
       <c r="Q240" t="n">
-        <v>1.369556</v>
+        <v>50.7242963</v>
       </c>
       <c r="R240" t="n">
         <v>577.96</v>
@@ -16102,10 +16102,10 @@
         <v>1.41107</v>
       </c>
       <c r="P241" t="n">
-        <v>1.411070411070411e-06</v>
+        <v>5.22618671e-05</v>
       </c>
       <c r="Q241" t="n">
-        <v>1.41107</v>
+        <v>52.2618519</v>
       </c>
       <c r="R241" t="n">
         <v>575.85</v>
@@ -16167,10 +16167,10 @@
         <v>1.463573</v>
       </c>
       <c r="P242" t="n">
-        <v>1.463573463573464e-06</v>
+        <v>5.42064246e-05</v>
       </c>
       <c r="Q242" t="n">
-        <v>1.463573</v>
+        <v>54.2064074</v>
       </c>
       <c r="R242" t="n">
         <v>461.13</v>
@@ -16232,10 +16232,10 @@
         <v>1.5116</v>
       </c>
       <c r="P243" t="n">
-        <v>1.511599511599512e-06</v>
+        <v>5.59851671e-05</v>
       </c>
       <c r="Q243" t="n">
-        <v>1.5116</v>
+        <v>55.9851852</v>
       </c>
       <c r="R243" t="n">
         <v>450.04</v>
@@ -16297,10 +16297,10 @@
         <v>1.562882</v>
       </c>
       <c r="P244" t="n">
-        <v>1.562881562881563e-06</v>
+        <v>5.78845023e-05</v>
       </c>
       <c r="Q244" t="n">
-        <v>1.562882</v>
+        <v>57.8845185</v>
       </c>
       <c r="R244" t="n">
         <v>573.38</v>
@@ -16362,10 +16362,10 @@
         <v>1.62149</v>
       </c>
       <c r="P245" t="n">
-        <v>1.621489621489621e-06</v>
+        <v>6.00551712e-05</v>
       </c>
       <c r="Q245" t="n">
-        <v>1.62149</v>
+        <v>60.0551852</v>
       </c>
       <c r="R245" t="n">
         <v>579.16</v>
@@ -16427,10 +16427,10 @@
         <v>1.683354</v>
       </c>
       <c r="P246" t="n">
-        <v>1.683353683353684e-06</v>
+        <v>6.23464327e-05</v>
       </c>
       <c r="Q246" t="n">
-        <v>1.683354</v>
+        <v>62.3464444</v>
       </c>
       <c r="R246" t="n">
         <v>510.94</v>
@@ -16492,10 +16492,10 @@
         <v>1.746032</v>
       </c>
       <c r="P247" t="n">
-        <v>1.746031746031746e-06</v>
+        <v>6.46678424e-05</v>
       </c>
       <c r="Q247" t="n">
-        <v>1.746032</v>
+        <v>64.6678519</v>
       </c>
       <c r="R247" t="n">
         <v>516.6</v>
@@ -16557,10 +16557,10 @@
         <v>1.810338</v>
       </c>
       <c r="P248" t="n">
-        <v>1.81033781033781e-06</v>
+        <v>6.70495485e-05</v>
       </c>
       <c r="Q248" t="n">
-        <v>1.810338</v>
+        <v>67.0495556</v>
       </c>
       <c r="R248" t="n">
         <v>582.36</v>
@@ -16622,10 +16622,10 @@
         <v>1.875458</v>
       </c>
       <c r="P249" t="n">
-        <v>1.875457875457875e-06</v>
+        <v>6.94614028e-05</v>
       </c>
       <c r="Q249" t="n">
-        <v>1.875458</v>
+        <v>69.4614074</v>
       </c>
       <c r="R249" t="n">
         <v>449.61</v>
@@ -16687,10 +16687,10 @@
         <v>1.251526</v>
       </c>
       <c r="P250" t="n">
-        <v>1.251526251526251e-06</v>
+        <v>4.63528241e-05</v>
       </c>
       <c r="Q250" t="n">
-        <v>1.251526</v>
+        <v>46.3528148</v>
       </c>
       <c r="R250" t="n">
         <v>456.66</v>
@@ -16752,10 +16752,10 @@
         <v>1.227513</v>
       </c>
       <c r="P251" t="n">
-        <v>1.227513227513228e-06</v>
+        <v>4.54634529e-05</v>
       </c>
       <c r="Q251" t="n">
-        <v>1.227513</v>
+        <v>45.4634444</v>
       </c>
       <c r="R251" t="n">
         <v>450.92</v>
@@ -16817,10 +16817,10 @@
         <v>1.200651</v>
       </c>
       <c r="P252" t="n">
-        <v>1.200651200651201e-06</v>
+        <v>4.4468563e-05</v>
       </c>
       <c r="Q252" t="n">
-        <v>1.200651</v>
+        <v>44.4685556</v>
       </c>
       <c r="R252" t="n">
         <v>396.28</v>
@@ -16882,10 +16882,10 @@
         <v>1.178673</v>
       </c>
       <c r="P253" t="n">
-        <v>1.178673178673179e-06</v>
+        <v>4.36545622e-05</v>
       </c>
       <c r="Q253" t="n">
-        <v>1.178673</v>
+        <v>43.6545556</v>
       </c>
       <c r="R253" t="n">
         <v>464.51</v>
@@ -16947,10 +16947,10 @@
         <v>1.1628</v>
       </c>
       <c r="P254" t="n">
-        <v>1.162800162800163e-06</v>
+        <v>4.30666727e-05</v>
       </c>
       <c r="Q254" t="n">
-        <v>1.1628</v>
+        <v>43.0666667</v>
       </c>
       <c r="R254" t="n">
         <v>454.25</v>
@@ -17012,10 +17012,10 @@
         <v>1.150997</v>
       </c>
       <c r="P255" t="n">
-        <v>1.150997150997151e-06</v>
+        <v>4.26295241e-05</v>
       </c>
       <c r="Q255" t="n">
-        <v>1.150997</v>
+        <v>42.6295185</v>
       </c>
       <c r="R255" t="n">
         <v>392.69</v>
@@ -17077,10 +17077,10 @@
         <v>1.145706</v>
       </c>
       <c r="P256" t="n">
-        <v>1.145706145706146e-06</v>
+        <v>4.2433561e-05</v>
       </c>
       <c r="Q256" t="n">
-        <v>1.145706</v>
+        <v>42.4335556</v>
       </c>
       <c r="R256" t="n">
         <v>405.21</v>
@@ -17142,10 +17142,10 @@
         <v>1.142043</v>
       </c>
       <c r="P257" t="n">
-        <v>1.142043142043142e-06</v>
+        <v>4.22978941e-05</v>
       </c>
       <c r="Q257" t="n">
-        <v>1.142043</v>
+        <v>42.2978889</v>
       </c>
       <c r="R257" t="n">
         <v>404.97</v>
@@ -17207,10 +17207,10 @@
         <v>1.140822</v>
       </c>
       <c r="P258" t="n">
-        <v>1.140822140822141e-06</v>
+        <v>4.22526719e-05</v>
       </c>
       <c r="Q258" t="n">
-        <v>1.140822</v>
+        <v>42.2526667</v>
       </c>
       <c r="R258" t="n">
         <v>522.92</v>
@@ -17272,10 +17272,10 @@
         <v>1.152218</v>
       </c>
       <c r="P259" t="n">
-        <v>1.152218152218152e-06</v>
+        <v>4.26747464e-05</v>
       </c>
       <c r="Q259" t="n">
-        <v>1.152218</v>
+        <v>42.6747407</v>
       </c>
       <c r="R259" t="n">
         <v>515.14</v>
@@ -17337,10 +17337,10 @@
         <v>1.166056</v>
       </c>
       <c r="P260" t="n">
-        <v>1.166056166056166e-06</v>
+        <v>4.31872654e-05</v>
       </c>
       <c r="Q260" t="n">
-        <v>1.166056</v>
+        <v>43.1872593</v>
       </c>
       <c r="R260" t="n">
         <v>454.81</v>
@@ -17402,10 +17402,10 @@
         <v>1.180708</v>
       </c>
       <c r="P261" t="n">
-        <v>1.180708180708181e-06</v>
+        <v>4.37299326e-05</v>
       </c>
       <c r="Q261" t="n">
-        <v>1.180708</v>
+        <v>43.7299259</v>
       </c>
       <c r="R261" t="n">
         <v>449.23</v>
@@ -17467,10 +17467,10 @@
         <v>1.204314</v>
       </c>
       <c r="P262" t="n">
-        <v>1.204314204314204e-06</v>
+        <v>4.46042298e-05</v>
       </c>
       <c r="Q262" t="n">
-        <v>1.204314</v>
+        <v>44.6042222</v>
       </c>
       <c r="R262" t="n">
         <v>511.89</v>
@@ -17532,10 +17532,10 @@
         <v>1.228327</v>
       </c>
       <c r="P263" t="n">
-        <v>1.228327228327228e-06</v>
+        <v>4.5493601e-05</v>
       </c>
       <c r="Q263" t="n">
-        <v>1.228327</v>
+        <v>45.4935926</v>
       </c>
       <c r="R263" t="n">
         <v>452.11</v>
@@ -17597,10 +17597,10 @@
         <v>1.258445</v>
       </c>
       <c r="P264" t="n">
-        <v>1.258445258445258e-06</v>
+        <v>4.66090836e-05</v>
       </c>
       <c r="Q264" t="n">
-        <v>1.258445</v>
+        <v>46.6090741</v>
       </c>
       <c r="R264" t="n">
         <v>453.14</v>
@@ -17662,10 +17662,10 @@
         <v>1.296703</v>
       </c>
       <c r="P265" t="n">
-        <v>1.296703296703297e-06</v>
+        <v>4.8026048e-05</v>
       </c>
       <c r="Q265" t="n">
-        <v>1.296703</v>
+        <v>48.026037</v>
       </c>
       <c r="R265" t="n">
         <v>458.3</v>
@@ -17727,10 +17727,10 @@
         <v>1.329263</v>
       </c>
       <c r="P266" t="n">
-        <v>1.329263329263329e-06</v>
+        <v>4.92319752e-05</v>
       </c>
       <c r="Q266" t="n">
-        <v>1.329263</v>
+        <v>49.231963</v>
       </c>
       <c r="R266" t="n">
         <v>524.61</v>
@@ -17792,10 +17792,10 @@
         <v>1.372812</v>
       </c>
       <c r="P267" t="n">
-        <v>1.372812372812373e-06</v>
+        <v>5.08449027e-05</v>
       </c>
       <c r="Q267" t="n">
-        <v>1.372812</v>
+        <v>50.8448889</v>
       </c>
       <c r="R267" t="n">
         <v>453.17</v>
@@ -17857,10 +17857,10 @@
         <v>1.415547</v>
       </c>
       <c r="P268" t="n">
-        <v>1.415547415547416e-06</v>
+        <v>5.24276821e-05</v>
       </c>
       <c r="Q268" t="n">
-        <v>1.415547</v>
+        <v>52.4276667</v>
       </c>
       <c r="R268" t="n">
         <v>523.34</v>
@@ -17922,10 +17922,10 @@
         <v>1.465201</v>
       </c>
       <c r="P269" t="n">
-        <v>1.465201465201465e-06</v>
+        <v>5.42667209e-05</v>
       </c>
       <c r="Q269" t="n">
-        <v>1.465201</v>
+        <v>54.2667037</v>
       </c>
       <c r="R269" t="n">
         <v>571.64</v>
@@ -17987,10 +17987,10 @@
         <v>1.514042</v>
       </c>
       <c r="P270" t="n">
-        <v>1.514041514041514e-06</v>
+        <v>5.60756116e-05</v>
       </c>
       <c r="Q270" t="n">
-        <v>1.514042</v>
+        <v>56.0756296</v>
       </c>
       <c r="R270" t="n">
         <v>517.73</v>
@@ -18052,10 +18052,10 @@
         <v>1.56451</v>
       </c>
       <c r="P271" t="n">
-        <v>1.564509564509564e-06</v>
+        <v>5.79447987e-05</v>
       </c>
       <c r="Q271" t="n">
-        <v>1.56451</v>
+        <v>57.9448148</v>
       </c>
       <c r="R271" t="n">
         <v>515.05</v>
@@ -18117,10 +18117,10 @@
         <v>1.62149</v>
       </c>
       <c r="P272" t="n">
-        <v>1.621489621489621e-06</v>
+        <v>6.00551712e-05</v>
       </c>
       <c r="Q272" t="n">
-        <v>1.62149</v>
+        <v>60.0551852</v>
       </c>
       <c r="R272" t="n">
         <v>461.9</v>
@@ -18182,10 +18182,10 @@
         <v>1.67847</v>
       </c>
       <c r="P273" t="n">
-        <v>1.678469678469679e-06</v>
+        <v>6.21655436e-05</v>
       </c>
       <c r="Q273" t="n">
-        <v>1.67847</v>
+        <v>62.1655556</v>
       </c>
       <c r="R273" t="n">
         <v>520.01</v>
@@ -18247,10 +18247,10 @@
         <v>1.737485</v>
       </c>
       <c r="P274" t="n">
-        <v>1.737484737484738e-06</v>
+        <v>6.43512866e-05</v>
       </c>
       <c r="Q274" t="n">
-        <v>1.737485</v>
+        <v>64.3512963</v>
       </c>
       <c r="R274" t="n">
         <v>515.51</v>
@@ -18312,10 +18312,10 @@
         <v>1.80057</v>
       </c>
       <c r="P275" t="n">
-        <v>1.800569800569801e-06</v>
+        <v>6.66877704e-05</v>
       </c>
       <c r="Q275" t="n">
-        <v>1.80057</v>
+        <v>66.6877778</v>
       </c>
       <c r="R275" t="n">
         <v>454.83</v>
@@ -18377,10 +18377,10 @@
         <v>1.867318</v>
       </c>
       <c r="P276" t="n">
-        <v>1.867317867317867e-06</v>
+        <v>6.9159921e-05</v>
       </c>
       <c r="Q276" t="n">
-        <v>1.867318</v>
+        <v>69.1599259</v>
       </c>
       <c r="R276" t="n">
         <v>392.3</v>
@@ -18442,10 +18442,10 @@
         <v>1.929996</v>
       </c>
       <c r="P277" t="n">
-        <v>1.92999592999593e-06</v>
+        <v>7.14813307e-05</v>
       </c>
       <c r="Q277" t="n">
-        <v>1.929996</v>
+        <v>71.4813333</v>
       </c>
       <c r="R277" t="n">
         <v>525.45</v>
@@ -18507,10 +18507,10 @@
         <v>1.995116</v>
       </c>
       <c r="P278" t="n">
-        <v>1.995115995115995e-06</v>
+        <v>7.3893185e-05</v>
       </c>
       <c r="Q278" t="n">
-        <v>1.995116</v>
+        <v>73.8931852</v>
       </c>
       <c r="R278" t="n">
         <v>514.21</v>
@@ -18572,10 +18572,10 @@
         <v>2.054538</v>
       </c>
       <c r="P279" t="n">
-        <v>2.054538054538055e-06</v>
+        <v>7.6094002e-05</v>
       </c>
       <c r="Q279" t="n">
-        <v>2.054538</v>
+        <v>76.094</v>
       </c>
       <c r="R279" t="n">
         <v>514.3</v>
@@ -18637,10 +18637,10 @@
         <v>2.118844</v>
       </c>
       <c r="P280" t="n">
-        <v>2.118844118844119e-06</v>
+        <v>7.84757081e-05</v>
       </c>
       <c r="Q280" t="n">
-        <v>2.118844</v>
+        <v>78.4757037</v>
       </c>
       <c r="R280" t="n">
         <v>515.54</v>
@@ -18702,10 +18702,10 @@
         <v>1.197395</v>
       </c>
       <c r="P281" t="n">
-        <v>1.197395197395197e-06</v>
+        <v>4.43479703e-05</v>
       </c>
       <c r="Q281" t="n">
-        <v>1.197395</v>
+        <v>44.347963</v>
       </c>
       <c r="R281" t="n">
         <v>511.81</v>
@@ -18767,10 +18767,10 @@
         <v>1.185592</v>
       </c>
       <c r="P282" t="n">
-        <v>1.185592185592186e-06</v>
+        <v>4.39108217e-05</v>
       </c>
       <c r="Q282" t="n">
-        <v>1.185592</v>
+        <v>43.9108148</v>
       </c>
       <c r="R282" t="n">
         <v>518.12</v>
@@ -18832,10 +18832,10 @@
         <v>1.177452</v>
       </c>
       <c r="P283" t="n">
-        <v>1.177452177452178e-06</v>
+        <v>4.36093399e-05</v>
       </c>
       <c r="Q283" t="n">
-        <v>1.177452</v>
+        <v>43.6093333</v>
       </c>
       <c r="R283" t="n">
         <v>515.88</v>
@@ -18897,10 +18897,10 @@
         <v>1.173789</v>
       </c>
       <c r="P284" t="n">
-        <v>1.173789173789174e-06</v>
+        <v>4.34736731e-05</v>
       </c>
       <c r="Q284" t="n">
-        <v>1.173789</v>
+        <v>43.4736667</v>
       </c>
       <c r="R284" t="n">
         <v>458.28</v>
@@ -18962,10 +18962,10 @@
         <v>1.176638</v>
       </c>
       <c r="P285" t="n">
-        <v>1.176638176638177e-06</v>
+        <v>4.35791917e-05</v>
       </c>
       <c r="Q285" t="n">
-        <v>1.176638</v>
+        <v>43.5791852</v>
       </c>
       <c r="R285" t="n">
         <v>464.78</v>
@@ -19027,10 +19027,10 @@
         <v>1.183964</v>
       </c>
       <c r="P286" t="n">
-        <v>1.183964183964184e-06</v>
+        <v>4.38505253e-05</v>
       </c>
       <c r="Q286" t="n">
-        <v>1.183964</v>
+        <v>43.8505185</v>
       </c>
       <c r="R286" t="n">
         <v>453.76</v>
@@ -19092,10 +19092,10 @@
         <v>1.194546</v>
       </c>
       <c r="P287" t="n">
-        <v>1.194546194546195e-06</v>
+        <v>4.42424516e-05</v>
       </c>
       <c r="Q287" t="n">
-        <v>1.194546</v>
+        <v>44.2424444</v>
       </c>
       <c r="R287" t="n">
         <v>396.58</v>
@@ -19157,10 +19157,10 @@
         <v>1.210012</v>
       </c>
       <c r="P288" t="n">
-        <v>1.21001221001221e-06</v>
+        <v>4.4815267e-05</v>
       </c>
       <c r="Q288" t="n">
-        <v>1.210012</v>
+        <v>44.8152593</v>
       </c>
       <c r="R288" t="n">
         <v>460.71</v>
@@ -19222,10 +19222,10 @@
         <v>1.229955</v>
       </c>
       <c r="P289" t="n">
-        <v>1.22995522995523e-06</v>
+        <v>4.55538974e-05</v>
       </c>
       <c r="Q289" t="n">
-        <v>1.229955</v>
+        <v>45.5538889</v>
       </c>
       <c r="R289" t="n">
         <v>453.92</v>
@@ -19287,10 +19287,10 @@
         <v>1.254375</v>
       </c>
       <c r="P290" t="n">
-        <v>1.254375254375254e-06</v>
+        <v>4.64583428e-05</v>
       </c>
       <c r="Q290" t="n">
-        <v>1.254375</v>
+        <v>46.4583333</v>
       </c>
       <c r="R290" t="n">
         <v>572.49</v>
@@ -19352,10 +19352,10 @@
         <v>1.282051</v>
       </c>
       <c r="P291" t="n">
-        <v>1.282051282051282e-06</v>
+        <v>4.74833808e-05</v>
       </c>
       <c r="Q291" t="n">
-        <v>1.282051</v>
+        <v>47.4833704</v>
       </c>
       <c r="R291" t="n">
         <v>578.86</v>
@@ -19417,10 +19417,10 @@
         <v>1.315832</v>
       </c>
       <c r="P292" t="n">
-        <v>1.315832315832316e-06</v>
+        <v>4.87345302e-05</v>
       </c>
       <c r="Q292" t="n">
-        <v>1.315832</v>
+        <v>48.7345185</v>
       </c>
       <c r="R292" t="n">
         <v>577.34</v>
@@ -19482,10 +19482,10 @@
         <v>1.35002</v>
       </c>
       <c r="P293" t="n">
-        <v>1.35002035002035e-06</v>
+        <v>5.00007537e-05</v>
       </c>
       <c r="Q293" t="n">
-        <v>1.35002</v>
+        <v>50.0007407</v>
       </c>
       <c r="R293" t="n">
         <v>458.21</v>
@@ -19547,10 +19547,10 @@
         <v>1.396825</v>
       </c>
       <c r="P294" t="n">
-        <v>1.396825396825397e-06</v>
+        <v>5.1734274e-05</v>
       </c>
       <c r="Q294" t="n">
-        <v>1.396825</v>
+        <v>51.7342593</v>
       </c>
       <c r="R294" t="n">
         <v>590.74</v>
@@ -19612,10 +19612,10 @@
         <v>1.433455</v>
       </c>
       <c r="P295" t="n">
-        <v>1.433455433455433e-06</v>
+        <v>5.3090942e-05</v>
       </c>
       <c r="Q295" t="n">
-        <v>1.433455</v>
+        <v>53.0909259</v>
       </c>
       <c r="R295" t="n">
         <v>577.13</v>
@@ -19677,10 +19677,10 @@
         <v>1.483109</v>
       </c>
       <c r="P296" t="n">
-        <v>1.483109483109483e-06</v>
+        <v>5.49299809e-05</v>
       </c>
       <c r="Q296" t="n">
-        <v>1.483109</v>
+        <v>54.929963</v>
       </c>
       <c r="R296" t="n">
         <v>399.65</v>
@@ -19742,10 +19742,10 @@
         <v>1.530729</v>
       </c>
       <c r="P297" t="n">
-        <v>1.530728530728531e-06</v>
+        <v>5.66936493e-05</v>
       </c>
       <c r="Q297" t="n">
-        <v>1.530729</v>
+        <v>56.6936667</v>
       </c>
       <c r="R297" t="n">
         <v>465.22</v>
@@ -19807,10 +19807,10 @@
         <v>1.580383</v>
       </c>
       <c r="P298" t="n">
-        <v>1.58038258038258e-06</v>
+        <v>5.85326882e-05</v>
       </c>
       <c r="Q298" t="n">
-        <v>1.580383</v>
+        <v>58.5327037</v>
       </c>
       <c r="R298" t="n">
         <v>573.2</v>
@@ -19872,10 +19872,10 @@
         <v>1.634514</v>
       </c>
       <c r="P299" t="n">
-        <v>1.634513634513635e-06</v>
+        <v>6.0537542e-05</v>
       </c>
       <c r="Q299" t="n">
-        <v>1.634514</v>
+        <v>60.5375556</v>
       </c>
       <c r="R299" t="n">
         <v>457.65</v>
@@ -19937,10 +19937,10 @@
         <v>1.689866</v>
       </c>
       <c r="P300" t="n">
-        <v>1.68986568986569e-06</v>
+        <v>6.25876181e-05</v>
       </c>
       <c r="Q300" t="n">
-        <v>1.689866</v>
+        <v>62.5876296</v>
       </c>
       <c r="R300" t="n">
         <v>527.84</v>
@@ -20002,10 +20002,10 @@
         <v>1.752951</v>
       </c>
       <c r="P301" t="n">
-        <v>1.752950752950753e-06</v>
+        <v>6.4924102e-05</v>
       </c>
       <c r="Q301" t="n">
-        <v>1.752951</v>
+        <v>64.9241111</v>
       </c>
       <c r="R301" t="n">
         <v>515.03</v>
@@ -20067,10 +20067,10 @@
         <v>1.813187</v>
       </c>
       <c r="P302" t="n">
-        <v>1.813186813186813e-06</v>
+        <v>6.71550672e-05</v>
       </c>
       <c r="Q302" t="n">
-        <v>1.813187</v>
+        <v>67.1550741</v>
       </c>
       <c r="R302" t="n">
         <v>515.5</v>
@@ -20132,10 +20132,10 @@
         <v>1.872202</v>
       </c>
       <c r="P303" t="n">
-        <v>1.872201872201872e-06</v>
+        <v>6.93408101e-05</v>
       </c>
       <c r="Q303" t="n">
-        <v>1.872202</v>
+        <v>69.3408148</v>
       </c>
       <c r="R303" t="n">
         <v>527.55</v>
@@ -20197,10 +20197,10 @@
         <v>1.934066</v>
       </c>
       <c r="P304" t="n">
-        <v>1.934065934065934e-06</v>
+        <v>7.16320716e-05</v>
       </c>
       <c r="Q304" t="n">
-        <v>1.934066</v>
+        <v>71.6320741</v>
       </c>
       <c r="R304" t="n">
         <v>455.91</v>
@@ -20262,10 +20262,10 @@
         <v>1.997965</v>
       </c>
       <c r="P305" t="n">
-        <v>1.997964997964998e-06</v>
+        <v>7.39987036e-05</v>
       </c>
       <c r="Q305" t="n">
-        <v>1.997965</v>
+        <v>73.9987037</v>
       </c>
       <c r="R305" t="n">
         <v>521.53</v>
@@ -20327,10 +20327,10 @@
         <v>2.057794</v>
       </c>
       <c r="P306" t="n">
-        <v>2.057794057794058e-06</v>
+        <v>7.62145947e-05</v>
       </c>
       <c r="Q306" t="n">
-        <v>2.057794</v>
+        <v>76.2145926</v>
       </c>
       <c r="R306" t="n">
         <v>456.28</v>
@@ -20392,10 +20392,10 @@
         <v>2.119658</v>
       </c>
       <c r="P307" t="n">
-        <v>2.11965811965812e-06</v>
+        <v>7.85058563e-05</v>
       </c>
       <c r="Q307" t="n">
-        <v>2.119658</v>
+        <v>78.5058519</v>
       </c>
       <c r="R307" t="n">
         <v>512.98</v>
@@ -20457,10 +20457,10 @@
         <v>2.17908</v>
       </c>
       <c r="P308" t="n">
-        <v>2.179080179080179e-06</v>
+        <v>8.07066733e-05</v>
       </c>
       <c r="Q308" t="n">
-        <v>2.17908</v>
+        <v>80.7066667</v>
       </c>
       <c r="R308" t="n">
         <v>573.76</v>
@@ -20522,10 +20522,10 @@
         <v>2.234432</v>
       </c>
       <c r="P309" t="n">
-        <v>2.234432234432235e-06</v>
+        <v>8.27567494e-05</v>
       </c>
       <c r="Q309" t="n">
-        <v>2.234432</v>
+        <v>82.7567407</v>
       </c>
       <c r="R309" t="n">
         <v>459.75</v>
@@ -20587,10 +20587,10 @@
         <v>2.292633</v>
       </c>
       <c r="P310" t="n">
-        <v>2.292633292633293e-06</v>
+        <v>8.49123442e-05</v>
       </c>
       <c r="Q310" t="n">
-        <v>2.292633</v>
+        <v>84.9123333</v>
       </c>
       <c r="R310" t="n">
         <v>587.84</v>
@@ -20652,10 +20652,10 @@
         <v>2.347578</v>
       </c>
       <c r="P311" t="n">
-        <v>2.347578347578348e-06</v>
+        <v>8.69473462e-05</v>
       </c>
       <c r="Q311" t="n">
-        <v>2.347578</v>
+        <v>86.9473333</v>
       </c>
       <c r="R311" t="n">
         <v>399.7</v>
@@ -20717,10 +20717,10 @@
         <v>1.224664</v>
       </c>
       <c r="P312" t="n">
-        <v>1.224664224664225e-06</v>
+        <v>4.53579342e-05</v>
       </c>
       <c r="Q312" t="n">
-        <v>1.224664</v>
+        <v>45.3579259</v>
       </c>
       <c r="R312" t="n">
         <v>452.05</v>
@@ -20782,10 +20782,10 @@
         <v>1.231583</v>
       </c>
       <c r="P313" t="n">
-        <v>1.231583231583232e-06</v>
+        <v>4.56141938e-05</v>
       </c>
       <c r="Q313" t="n">
-        <v>1.231583</v>
+        <v>45.6141852</v>
       </c>
       <c r="R313" t="n">
         <v>514.8</v>
@@ -20847,10 +20847,10 @@
         <v>1.239723</v>
       </c>
       <c r="P314" t="n">
-        <v>1.23972323972324e-06</v>
+        <v>4.59156755e-05</v>
       </c>
       <c r="Q314" t="n">
-        <v>1.239723</v>
+        <v>45.9156667</v>
       </c>
       <c r="R314" t="n">
         <v>453.95</v>
@@ -20912,10 +20912,10 @@
         <v>1.25234</v>
       </c>
       <c r="P315" t="n">
-        <v>1.252340252340252e-06</v>
+        <v>4.63829723e-05</v>
       </c>
       <c r="Q315" t="n">
-        <v>1.25234</v>
+        <v>46.382963</v>
       </c>
       <c r="R315" t="n">
         <v>457.85</v>
@@ -20977,10 +20977,10 @@
         <v>1.27269</v>
       </c>
       <c r="P316" t="n">
-        <v>1.272690272690273e-06</v>
+        <v>4.71366768e-05</v>
       </c>
       <c r="Q316" t="n">
-        <v>1.27269</v>
+        <v>47.1366667</v>
       </c>
       <c r="R316" t="n">
         <v>522.4299999999999</v>
@@ -21042,10 +21042,10 @@
         <v>1.28897</v>
       </c>
       <c r="P317" t="n">
-        <v>1.288970288970289e-06</v>
+        <v>4.77396403e-05</v>
       </c>
       <c r="Q317" t="n">
-        <v>1.28897</v>
+        <v>47.7396296</v>
       </c>
       <c r="R317" t="n">
         <v>453.37</v>
@@ -21107,10 +21107,10 @@
         <v>1.319088</v>
       </c>
       <c r="P318" t="n">
-        <v>1.319088319088319e-06</v>
+        <v>4.88551229e-05</v>
       </c>
       <c r="Q318" t="n">
-        <v>1.319088</v>
+        <v>48.8551111</v>
       </c>
       <c r="R318" t="n">
         <v>453.59</v>
@@ -21172,10 +21172,10 @@
         <v>1.350427</v>
       </c>
       <c r="P319" t="n">
-        <v>1.35042735042735e-06</v>
+        <v>5.00158278e-05</v>
       </c>
       <c r="Q319" t="n">
-        <v>1.350427</v>
+        <v>50.0158148</v>
       </c>
       <c r="R319" t="n">
         <v>453.8</v>
@@ -21237,10 +21237,10 @@
         <v>1.387057</v>
       </c>
       <c r="P320" t="n">
-        <v>1.387057387057387e-06</v>
+        <v>5.13724958e-05</v>
       </c>
       <c r="Q320" t="n">
-        <v>1.387057</v>
+        <v>51.3724815</v>
       </c>
       <c r="R320" t="n">
         <v>458.53</v>
@@ -21302,10 +21302,10 @@
         <v>1.422873</v>
       </c>
       <c r="P321" t="n">
-        <v>1.422873422873423e-06</v>
+        <v>5.26990157e-05</v>
       </c>
       <c r="Q321" t="n">
-        <v>1.422873</v>
+        <v>52.699</v>
       </c>
       <c r="R321" t="n">
         <v>510.94</v>
@@ -21367,10 +21367,10 @@
         <v>1.462759</v>
       </c>
       <c r="P322" t="n">
-        <v>1.462759462759463e-06</v>
+        <v>5.41762764e-05</v>
       </c>
       <c r="Q322" t="n">
-        <v>1.462759</v>
+        <v>54.1762593</v>
       </c>
       <c r="R322" t="n">
         <v>578.71</v>
@@ -21432,10 +21432,10 @@
         <v>1.504681</v>
       </c>
       <c r="P323" t="n">
-        <v>1.504680504680505e-06</v>
+        <v>5.57289076e-05</v>
       </c>
       <c r="Q323" t="n">
-        <v>1.504681</v>
+        <v>55.7289259</v>
       </c>
       <c r="R323" t="n">
         <v>519.27</v>
@@ -21497,10 +21497,10 @@
         <v>1.557998</v>
       </c>
       <c r="P324" t="n">
-        <v>1.557997557997558e-06</v>
+        <v>5.77036133e-05</v>
       </c>
       <c r="Q324" t="n">
-        <v>1.557998</v>
+        <v>57.7036296</v>
       </c>
       <c r="R324" t="n">
         <v>456.02</v>
@@ -21562,10 +21562,10 @@
         <v>1.601547</v>
       </c>
       <c r="P325" t="n">
-        <v>1.601546601546602e-06</v>
+        <v>5.93165408e-05</v>
       </c>
       <c r="Q325" t="n">
-        <v>1.601547</v>
+        <v>59.3165556</v>
       </c>
       <c r="R325" t="n">
         <v>461.39</v>
@@ -21627,10 +21627,10 @@
         <v>1.659341</v>
       </c>
       <c r="P326" t="n">
-        <v>1.659340659340659e-06</v>
+        <v>6.14570615e-05</v>
       </c>
       <c r="Q326" t="n">
-        <v>1.659341</v>
+        <v>61.4570741</v>
       </c>
       <c r="R326" t="n">
         <v>517.6799999999999</v>
@@ -21692,10 +21692,10 @@
         <v>1.7151</v>
       </c>
       <c r="P327" t="n">
-        <v>1.715099715099715e-06</v>
+        <v>6.35222117e-05</v>
       </c>
       <c r="Q327" t="n">
-        <v>1.7151</v>
+        <v>63.5222222</v>
       </c>
       <c r="R327" t="n">
         <v>573.51</v>
@@ -21757,10 +21757,10 @@
         <v>1.765568</v>
       </c>
       <c r="P328" t="n">
-        <v>1.765567765567765e-06</v>
+        <v>6.53913987e-05</v>
       </c>
       <c r="Q328" t="n">
-        <v>1.765568</v>
+        <v>65.3914074</v>
       </c>
       <c r="R328" t="n">
         <v>459.93</v>
@@ -21822,10 +21822,10 @@
         <v>1.824176</v>
       </c>
       <c r="P329" t="n">
-        <v>1.824175824175824e-06</v>
+        <v>6.75620676e-05</v>
       </c>
       <c r="Q329" t="n">
-        <v>1.824176</v>
+        <v>67.5620741</v>
       </c>
       <c r="R329" t="n">
         <v>398.43</v>
@@ -21887,10 +21887,10 @@
         <v>1.88197</v>
       </c>
       <c r="P330" t="n">
-        <v>1.881969881969882e-06</v>
+        <v>6.97025882e-05</v>
       </c>
       <c r="Q330" t="n">
-        <v>1.88197</v>
+        <v>69.7025926</v>
       </c>
       <c r="R330" t="n">
         <v>524.13</v>
@@ -21952,10 +21952,10 @@
         <v>1.943834</v>
       </c>
       <c r="P331" t="n">
-        <v>1.943833943833944e-06</v>
+        <v>7.19938498e-05</v>
       </c>
       <c r="Q331" t="n">
-        <v>1.943834</v>
+        <v>71.9938519</v>
       </c>
       <c r="R331" t="n">
         <v>454.11</v>
@@ -22017,10 +22017,10 @@
         <v>2.007326</v>
       </c>
       <c r="P332" t="n">
-        <v>2.007326007326007e-06</v>
+        <v>7.43454077e-05</v>
       </c>
       <c r="Q332" t="n">
-        <v>2.007326</v>
+        <v>74.3454074</v>
       </c>
       <c r="R332" t="n">
         <v>450.89</v>
@@ -22082,10 +22082,10 @@
         <v>2.066341</v>
       </c>
       <c r="P333" t="n">
-        <v>2.066341066341066e-06</v>
+        <v>7.65311506e-05</v>
       </c>
       <c r="Q333" t="n">
-        <v>2.066341</v>
+        <v>76.5311481</v>
       </c>
       <c r="R333" t="n">
         <v>575.46</v>
@@ -22147,10 +22147,10 @@
         <v>2.126577</v>
       </c>
       <c r="P334" t="n">
-        <v>2.126577126577127e-06</v>
+        <v>7.87621158e-05</v>
       </c>
       <c r="Q334" t="n">
-        <v>2.126577</v>
+        <v>78.7621111</v>
       </c>
       <c r="R334" t="n">
         <v>578.54</v>
@@ -22212,10 +22212,10 @@
         <v>2.188034</v>
       </c>
       <c r="P335" t="n">
-        <v>2.188034188034188e-06</v>
+        <v>8.10383033e-05</v>
       </c>
       <c r="Q335" t="n">
-        <v>2.188034</v>
+        <v>81.0382963</v>
       </c>
       <c r="R335" t="n">
         <v>460.91</v>
@@ -22277,10 +22277,10 @@
         <v>2.242572</v>
       </c>
       <c r="P336" t="n">
-        <v>2.242572242572243e-06</v>
+        <v>8.30582312e-05</v>
       </c>
       <c r="Q336" t="n">
-        <v>2.242572</v>
+        <v>83.0582222</v>
       </c>
       <c r="R336" t="n">
         <v>589.3099999999999</v>
@@ -22342,10 +22342,10 @@
         <v>2.300366</v>
       </c>
       <c r="P337" t="n">
-        <v>2.3003663003663e-06</v>
+        <v>8.51987519e-05</v>
       </c>
       <c r="Q337" t="n">
-        <v>2.300366</v>
+        <v>85.1987407</v>
       </c>
       <c r="R337" t="n">
         <v>456.75</v>
@@ -22407,10 +22407,10 @@
         <v>2.352055</v>
       </c>
       <c r="P338" t="n">
-        <v>2.352055352055352e-06</v>
+        <v>8.71131612e-05</v>
       </c>
       <c r="Q338" t="n">
-        <v>2.352055</v>
+        <v>87.1131481</v>
       </c>
       <c r="R338" t="n">
         <v>514.1900000000001</v>
@@ -22472,10 +22472,10 @@
         <v>2.405372</v>
       </c>
       <c r="P339" t="n">
-        <v>2.405372405372405e-06</v>
+        <v>8.90878669e-05</v>
       </c>
       <c r="Q339" t="n">
-        <v>2.405372</v>
+        <v>89.0878519</v>
       </c>
       <c r="R339" t="n">
         <v>451.11</v>
@@ -22537,10 +22537,10 @@
         <v>2.457468</v>
       </c>
       <c r="P340" t="n">
-        <v>2.457468457468458e-06</v>
+        <v>9.10173503e-05</v>
       </c>
       <c r="Q340" t="n">
-        <v>2.457468</v>
+        <v>91.0173333</v>
       </c>
       <c r="R340" t="n">
         <v>577.86</v>
@@ -22602,10 +22602,10 @@
         <v>2.500204</v>
       </c>
       <c r="P341" t="n">
-        <v>2.5002035002035e-06</v>
+        <v>9.26001296e-05</v>
       </c>
       <c r="Q341" t="n">
-        <v>2.500204</v>
+        <v>92.6001481</v>
       </c>
       <c r="R341" t="n">
         <v>513.35</v>
@@ -22667,10 +22667,10 @@
         <v>2.554335</v>
       </c>
       <c r="P342" t="n">
-        <v>2.554334554334554e-06</v>
+        <v>9.46049835e-05</v>
       </c>
       <c r="Q342" t="n">
-        <v>2.554335</v>
+        <v>94.605</v>
       </c>
       <c r="R342" t="n">
         <v>457.58</v>
@@ -22732,10 +22732,10 @@
         <v>1.343101</v>
       </c>
       <c r="P343" t="n">
-        <v>1.343101343101343e-06</v>
+        <v>4.97444942e-05</v>
       </c>
       <c r="Q343" t="n">
-        <v>1.343101</v>
+        <v>49.7444815</v>
       </c>
       <c r="R343" t="n">
         <v>400.44</v>
@@ -22797,10 +22797,10 @@
         <v>1.362637</v>
       </c>
       <c r="P344" t="n">
-        <v>1.362637362637363e-06</v>
+        <v>5.04680505e-05</v>
       </c>
       <c r="Q344" t="n">
-        <v>1.362637</v>
+        <v>50.468037</v>
       </c>
       <c r="R344" t="n">
         <v>584.74</v>
@@ -22862,10 +22862,10 @@
         <v>1.383801</v>
       </c>
       <c r="P345" t="n">
-        <v>1.383801383801384e-06</v>
+        <v>5.12519031e-05</v>
       </c>
       <c r="Q345" t="n">
-        <v>1.383801</v>
+        <v>51.2518889</v>
       </c>
       <c r="R345" t="n">
         <v>519.5700000000001</v>
@@ -22927,10 +22927,10 @@
         <v>1.406593</v>
       </c>
       <c r="P346" t="n">
-        <v>1.406593406593407e-06</v>
+        <v>5.20960521e-05</v>
       </c>
       <c r="Q346" t="n">
-        <v>1.406593</v>
+        <v>52.096037</v>
       </c>
       <c r="R346" t="n">
         <v>393.28</v>
@@ -22992,10 +22992,10 @@
         <v>1.441595</v>
       </c>
       <c r="P347" t="n">
-        <v>1.441595441595442e-06</v>
+        <v>5.33924238e-05</v>
       </c>
       <c r="Q347" t="n">
-        <v>1.441595</v>
+        <v>53.3924074</v>
       </c>
       <c r="R347" t="n">
         <v>445.99</v>
@@ -23057,10 +23057,10 @@
         <v>1.474969</v>
       </c>
       <c r="P348" t="n">
-        <v>1.474969474969475e-06</v>
+        <v>5.46284991e-05</v>
       </c>
       <c r="Q348" t="n">
-        <v>1.474969</v>
+        <v>54.6284815</v>
       </c>
       <c r="R348" t="n">
         <v>516.59</v>
@@ -23122,10 +23122,10 @@
         <v>1.509972</v>
       </c>
       <c r="P349" t="n">
-        <v>1.50997150997151e-06</v>
+        <v>5.59248707e-05</v>
       </c>
       <c r="Q349" t="n">
-        <v>1.509972</v>
+        <v>55.9248889</v>
       </c>
       <c r="R349" t="n">
         <v>581.3</v>
@@ -23187,10 +23187,10 @@
         <v>1.555556</v>
       </c>
       <c r="P350" t="n">
-        <v>1.555555555555556e-06</v>
+        <v>5.76131687e-05</v>
       </c>
       <c r="Q350" t="n">
-        <v>1.555556</v>
+        <v>57.6131852</v>
       </c>
       <c r="R350" t="n">
         <v>519.04</v>
@@ -23252,10 +23252,10 @@
         <v>1.593814</v>
       </c>
       <c r="P351" t="n">
-        <v>1.593813593813594e-06</v>
+        <v>5.90301331e-05</v>
       </c>
       <c r="Q351" t="n">
-        <v>1.593814</v>
+        <v>59.0301481</v>
       </c>
       <c r="R351" t="n">
         <v>514.12</v>
@@ -23317,10 +23317,10 @@
         <v>1.639805</v>
       </c>
       <c r="P352" t="n">
-        <v>1.63980463980464e-06</v>
+        <v>6.07335052e-05</v>
       </c>
       <c r="Q352" t="n">
-        <v>1.639805</v>
+        <v>60.7335185</v>
       </c>
       <c r="R352" t="n">
         <v>583.95</v>
@@ -23382,10 +23382,10 @@
         <v>1.691494</v>
       </c>
       <c r="P353" t="n">
-        <v>1.691493691493691e-06</v>
+        <v>6.26479145e-05</v>
       </c>
       <c r="Q353" t="n">
-        <v>1.691494</v>
+        <v>62.6479259</v>
       </c>
       <c r="R353" t="n">
         <v>577.98</v>
@@ -23447,10 +23447,10 @@
         <v>1.740741</v>
       </c>
       <c r="P354" t="n">
-        <v>1.740740740740741e-06</v>
+        <v>6.44718793e-05</v>
       </c>
       <c r="Q354" t="n">
-        <v>1.740741</v>
+        <v>64.4718889</v>
       </c>
       <c r="R354" t="n">
         <v>455.18</v>
@@ -23512,10 +23512,10 @@
         <v>1.794872</v>
       </c>
       <c r="P355" t="n">
-        <v>1.794871794871795e-06</v>
+        <v>6.64767331e-05</v>
       </c>
       <c r="Q355" t="n">
-        <v>1.794872</v>
+        <v>66.4767407</v>
       </c>
       <c r="R355" t="n">
         <v>514.76</v>
@@ -23577,10 +23577,10 @@
         <v>1.851852</v>
       </c>
       <c r="P356" t="n">
-        <v>1.851851851851852e-06</v>
+        <v>6.85871056e-05</v>
       </c>
       <c r="Q356" t="n">
-        <v>1.851852</v>
+        <v>68.5871111</v>
       </c>
       <c r="R356" t="n">
         <v>521</v>
@@ -23642,10 +23642,10 @@
         <v>1.903541</v>
       </c>
       <c r="P357" t="n">
-        <v>1.903540903540903e-06</v>
+        <v>7.05015149e-05</v>
       </c>
       <c r="Q357" t="n">
-        <v>1.903541</v>
+        <v>70.5015185</v>
       </c>
       <c r="R357" t="n">
         <v>513.08</v>
@@ -23707,10 +23707,10 @@
         <v>1.960521</v>
       </c>
       <c r="P358" t="n">
-        <v>1.960520960520961e-06</v>
+        <v>7.26118874e-05</v>
       </c>
       <c r="Q358" t="n">
-        <v>1.960521</v>
+        <v>72.6118889</v>
       </c>
       <c r="R358" t="n">
         <v>516.97</v>
@@ -23772,10 +23772,10 @@
         <v>2.021164</v>
       </c>
       <c r="P359" t="n">
-        <v>2.021164021164021e-06</v>
+        <v>7.48579267e-05</v>
       </c>
       <c r="Q359" t="n">
-        <v>2.021164</v>
+        <v>74.8579259</v>
       </c>
       <c r="R359" t="n">
         <v>515.6900000000001</v>
@@ -23837,10 +23837,10 @@
         <v>2.072853</v>
       </c>
       <c r="P360" t="n">
-        <v>2.072853072853073e-06</v>
+        <v>7.6772336e-05</v>
       </c>
       <c r="Q360" t="n">
-        <v>2.072853</v>
+        <v>76.7723333</v>
       </c>
       <c r="R360" t="n">
         <v>517.65</v>
@@ -23902,10 +23902,10 @@
         <v>2.129426</v>
       </c>
       <c r="P361" t="n">
-        <v>2.129426129426129e-06</v>
+        <v>7.88676344e-05</v>
       </c>
       <c r="Q361" t="n">
-        <v>2.129426</v>
+        <v>78.8676296</v>
       </c>
       <c r="R361" t="n">
         <v>516.09</v>
@@ -23967,10 +23967,10 @@
         <v>2.192104</v>
       </c>
       <c r="P362" t="n">
-        <v>2.192104192104192e-06</v>
+        <v>8.11890442e-05</v>
       </c>
       <c r="Q362" t="n">
-        <v>2.192104</v>
+        <v>81.189037</v>
       </c>
       <c r="R362" t="n">
         <v>580.14</v>
@@ -24032,10 +24032,10 @@
         <v>2.24827</v>
       </c>
       <c r="P363" t="n">
-        <v>2.248270248270248e-06</v>
+        <v>8.32692685e-05</v>
       </c>
       <c r="Q363" t="n">
-        <v>2.24827</v>
+        <v>83.2692593</v>
       </c>
       <c r="R363" t="n">
         <v>456.81</v>
@@ -24097,10 +24097,10 @@
         <v>2.311355</v>
       </c>
       <c r="P364" t="n">
-        <v>2.311355311355311e-06</v>
+        <v>8.56057523e-05</v>
       </c>
       <c r="Q364" t="n">
-        <v>2.311355</v>
+        <v>85.6057407</v>
       </c>
       <c r="R364" t="n">
         <v>514.01</v>
@@ -24162,10 +24162,10 @@
         <v>2.35816</v>
       </c>
       <c r="P365" t="n">
-        <v>2.358160358160358e-06</v>
+        <v>8.73392725e-05</v>
       </c>
       <c r="Q365" t="n">
-        <v>2.35816</v>
+        <v>87.3392593</v>
       </c>
       <c r="R365" t="n">
         <v>509.05</v>
@@ -24227,10 +24227,10 @@
         <v>2.406593</v>
       </c>
       <c r="P366" t="n">
-        <v>2.406593406593407e-06</v>
+        <v>8.91330891e-05</v>
       </c>
       <c r="Q366" t="n">
-        <v>2.406593</v>
+        <v>89.1330741</v>
       </c>
       <c r="R366" t="n">
         <v>518.01</v>
@@ -24292,10 +24292,10 @@
         <v>2.460724</v>
       </c>
       <c r="P367" t="n">
-        <v>2.460724460724461e-06</v>
+        <v>9.1137943e-05</v>
       </c>
       <c r="Q367" t="n">
-        <v>2.460724</v>
+        <v>91.1379259</v>
       </c>
       <c r="R367" t="n">
         <v>511.15</v>
@@ -24357,10 +24357,10 @@
         <v>2.505902</v>
       </c>
       <c r="P368" t="n">
-        <v>2.505901505901506e-06</v>
+        <v>9.28111669e-05</v>
       </c>
       <c r="Q368" t="n">
-        <v>2.505902</v>
+        <v>92.8111852</v>
       </c>
       <c r="R368" t="n">
         <v>515.85</v>
@@ -24422,10 +24422,10 @@
         <v>2.555963</v>
       </c>
       <c r="P369" t="n">
-        <v>2.555962555962556e-06</v>
+        <v>9.46652799e-05</v>
       </c>
       <c r="Q369" t="n">
-        <v>2.555963</v>
+        <v>94.6652963</v>
       </c>
       <c r="R369" t="n">
         <v>518.45</v>
@@ -24487,10 +24487,10 @@
         <v>2.602361</v>
       </c>
       <c r="P370" t="n">
-        <v>2.602360602360603e-06</v>
+        <v>9.6383726e-05</v>
       </c>
       <c r="Q370" t="n">
-        <v>2.602361</v>
+        <v>96.3837407</v>
       </c>
       <c r="R370" t="n">
         <v>392.41</v>
@@ -24552,10 +24552,10 @@
         <v>2.64591</v>
       </c>
       <c r="P371" t="n">
-        <v>2.645909645909646e-06</v>
+        <v>9.79966536e-05</v>
       </c>
       <c r="Q371" t="n">
-        <v>2.64591</v>
+        <v>97.9966667</v>
       </c>
       <c r="R371" t="n">
         <v>592.3099999999999</v>
@@ -24617,10 +24617,10 @@
         <v>2.689459</v>
       </c>
       <c r="P372" t="n">
-        <v>2.689458689458689e-06</v>
+        <v>9.96095811e-05</v>
       </c>
       <c r="Q372" t="n">
-        <v>2.689459</v>
+        <v>99.6095926</v>
       </c>
       <c r="R372" t="n">
         <v>452.83</v>
@@ -24682,10 +24682,10 @@
         <v>2.731787</v>
       </c>
       <c r="P373" t="n">
-        <v>2.731786731786732e-06</v>
+        <v>0.000101177286</v>
       </c>
       <c r="Q373" t="n">
-        <v>2.731787</v>
+        <v>101.177296</v>
       </c>
       <c r="R373" t="n">
         <v>512.21</v>
@@ -24747,10 +24747,10 @@
         <v>1.578348</v>
       </c>
       <c r="P374" t="n">
-        <v>1.578347578347578e-06</v>
+        <v>5.84573177e-05</v>
       </c>
       <c r="Q374" t="n">
-        <v>1.578348</v>
+        <v>58.4573333</v>
       </c>
       <c r="R374" t="n">
         <v>514.73</v>
@@ -24812,10 +24812,10 @@
         <v>1.604396</v>
       </c>
       <c r="P375" t="n">
-        <v>1.604395604395604e-06</v>
+        <v>5.94220594e-05</v>
       </c>
       <c r="Q375" t="n">
-        <v>1.604396</v>
+        <v>59.4220741</v>
       </c>
       <c r="R375" t="n">
         <v>515.79</v>
@@ -24877,10 +24877,10 @@
         <v>1.631258</v>
       </c>
       <c r="P376" t="n">
-        <v>1.631257631257631e-06</v>
+        <v>6.04169493e-05</v>
       </c>
       <c r="Q376" t="n">
-        <v>1.631258</v>
+        <v>60.416963</v>
       </c>
       <c r="R376" t="n">
         <v>510.59</v>
@@ -24942,10 +24942,10 @@
         <v>1.665446</v>
       </c>
       <c r="P377" t="n">
-        <v>1.665445665445665e-06</v>
+        <v>6.16831728e-05</v>
       </c>
       <c r="Q377" t="n">
-        <v>1.665446</v>
+        <v>61.6831852</v>
       </c>
       <c r="R377" t="n">
         <v>579.36</v>
@@ -25007,10 +25007,10 @@
         <v>1.699634</v>
       </c>
       <c r="P378" t="n">
-        <v>1.6996336996337e-06</v>
+        <v>6.29493963e-05</v>
       </c>
       <c r="Q378" t="n">
-        <v>1.699634</v>
+        <v>62.9494074</v>
       </c>
       <c r="R378" t="n">
         <v>455</v>
@@ -25072,10 +25072,10 @@
         <v>1.731787</v>
       </c>
       <c r="P379" t="n">
-        <v>1.731786731786732e-06</v>
+        <v>6.41402493e-05</v>
       </c>
       <c r="Q379" t="n">
-        <v>1.731787</v>
+        <v>64.1402593</v>
       </c>
       <c r="R379" t="n">
         <v>523.45</v>
@@ -25137,10 +25137,10 @@
         <v>1.775336</v>
       </c>
       <c r="P380" t="n">
-        <v>1.775335775335775e-06</v>
+        <v>6.57531769e-05</v>
       </c>
       <c r="Q380" t="n">
-        <v>1.775336</v>
+        <v>65.7531852</v>
       </c>
       <c r="R380" t="n">
         <v>515.63</v>
@@ -25202,10 +25202,10 @@
         <v>1.818071</v>
       </c>
       <c r="P381" t="n">
-        <v>1.818070818070818e-06</v>
+        <v>6.73359562e-05</v>
       </c>
       <c r="Q381" t="n">
-        <v>1.818071</v>
+        <v>67.335963</v>
       </c>
       <c r="R381" t="n">
         <v>579.23</v>
@@ -25267,10 +25267,10 @@
         <v>1.858771</v>
       </c>
       <c r="P382" t="n">
-        <v>1.858770858770859e-06</v>
+        <v>6.88433651e-05</v>
       </c>
       <c r="Q382" t="n">
-        <v>1.858771</v>
+        <v>68.8433704</v>
       </c>
       <c r="R382" t="n">
         <v>455.93</v>
@@ -25332,10 +25332,10 @@
         <v>1.900692</v>
       </c>
       <c r="P383" t="n">
-        <v>1.900691900691901e-06</v>
+        <v>7.03959963e-05</v>
       </c>
       <c r="Q383" t="n">
-        <v>1.900692</v>
+        <v>70.396</v>
       </c>
       <c r="R383" t="n">
         <v>524.6799999999999</v>
@@ -25397,10 +25397,10 @@
         <v>1.95116</v>
       </c>
       <c r="P384" t="n">
-        <v>1.951159951159951e-06</v>
+        <v>7.22651834e-05</v>
       </c>
       <c r="Q384" t="n">
-        <v>1.95116</v>
+        <v>72.2651852</v>
       </c>
       <c r="R384" t="n">
         <v>451.54</v>
@@ -25462,10 +25462,10 @@
         <v>1.999186</v>
       </c>
       <c r="P385" t="n">
-        <v>1.999185999185999e-06</v>
+        <v>7.40439259e-05</v>
       </c>
       <c r="Q385" t="n">
-        <v>1.999186</v>
+        <v>74.0439259</v>
       </c>
       <c r="R385" t="n">
         <v>576.59</v>
@@ -25527,10 +25527,10 @@
         <v>2.045584</v>
       </c>
       <c r="P386" t="n">
-        <v>2.045584045584045e-06</v>
+        <v>7.57623721e-05</v>
       </c>
       <c r="Q386" t="n">
-        <v>2.045584</v>
+        <v>75.7623704</v>
       </c>
       <c r="R386" t="n">
         <v>517.92</v>
@@ -25592,10 +25592,10 @@
         <v>2.09768</v>
       </c>
       <c r="P387" t="n">
-        <v>2.097680097680098e-06</v>
+        <v>7.76918555e-05</v>
       </c>
       <c r="Q387" t="n">
-        <v>2.09768</v>
+        <v>77.6918519</v>
       </c>
       <c r="R387" t="n">
         <v>395.98</v>
@@ -25657,10 +25657,10 @@
         <v>2.151404</v>
       </c>
       <c r="P388" t="n">
-        <v>2.151404151404151e-06</v>
+        <v>7.96816352e-05</v>
       </c>
       <c r="Q388" t="n">
-        <v>2.151404</v>
+        <v>79.6816296</v>
       </c>
       <c r="R388" t="n">
         <v>404.86</v>
@@ -25722,10 +25722,10 @@
         <v>2.201872</v>
       </c>
       <c r="P389" t="n">
-        <v>2.201872201872202e-06</v>
+        <v>8.15508223e-05</v>
       </c>
       <c r="Q389" t="n">
-        <v>2.201872</v>
+        <v>81.5508148</v>
       </c>
       <c r="R389" t="n">
         <v>585.1900000000001</v>
@@ -25787,10 +25787,10 @@
         <v>2.250305</v>
       </c>
       <c r="P390" t="n">
-        <v>2.25030525030525e-06</v>
+        <v>8.33446389e-05</v>
       </c>
       <c r="Q390" t="n">
-        <v>2.250305</v>
+        <v>83.3446296</v>
       </c>
       <c r="R390" t="n">
         <v>579.0700000000001</v>
@@ -25852,10 +25852,10 @@
         <v>2.30932</v>
       </c>
       <c r="P391" t="n">
-        <v>2.309320309320309e-06</v>
+        <v>8.55303818e-05</v>
       </c>
       <c r="Q391" t="n">
-        <v>2.30932</v>
+        <v>85.5303704</v>
       </c>
       <c r="R391" t="n">
         <v>454.84</v>
@@ -25917,10 +25917,10 @@
         <v>2.359788</v>
       </c>
       <c r="P392" t="n">
-        <v>2.35978835978836e-06</v>
+        <v>8.73995689e-05</v>
       </c>
       <c r="Q392" t="n">
-        <v>2.359788</v>
+        <v>87.3995556</v>
       </c>
       <c r="R392" t="n">
         <v>512.89</v>
@@ -25982,10 +25982,10 @@
         <v>2.412698</v>
       </c>
       <c r="P393" t="n">
-        <v>2.412698412698413e-06</v>
+        <v>8.93592005e-05</v>
       </c>
       <c r="Q393" t="n">
-        <v>2.412698</v>
+        <v>89.3591852</v>
       </c>
       <c r="R393" t="n">
         <v>580.12</v>
@@ -26047,10 +26047,10 @@
         <v>2.464794</v>
       </c>
       <c r="P394" t="n">
-        <v>2.464794464794465e-06</v>
+        <v>9.12886839e-05</v>
       </c>
       <c r="Q394" t="n">
-        <v>2.464794</v>
+        <v>91.2886667</v>
       </c>
       <c r="R394" t="n">
         <v>516.2</v>
@@ -26112,10 +26112,10 @@
         <v>2.502239</v>
       </c>
       <c r="P395" t="n">
-        <v>2.502238502238503e-06</v>
+        <v>9.26755001e-05</v>
       </c>
       <c r="Q395" t="n">
-        <v>2.502239</v>
+        <v>92.6755185</v>
       </c>
       <c r="R395" t="n">
         <v>519.6799999999999</v>
@@ -26177,10 +26177,10 @@
         <v>2.558405</v>
       </c>
       <c r="P396" t="n">
-        <v>2.558404558404558e-06</v>
+        <v>9.47557244e-05</v>
       </c>
       <c r="Q396" t="n">
-        <v>2.558405</v>
+        <v>94.7557407</v>
       </c>
       <c r="R396" t="n">
         <v>458.97</v>
@@ -26242,10 +26242,10 @@
         <v>2.600733</v>
       </c>
       <c r="P397" t="n">
-        <v>2.600732600732601e-06</v>
+        <v>9.63234297e-05</v>
       </c>
       <c r="Q397" t="n">
-        <v>2.600733</v>
+        <v>96.3234444</v>
       </c>
       <c r="R397" t="n">
         <v>514.09</v>
@@ -26307,10 +26307,10 @@
         <v>2.648759</v>
       </c>
       <c r="P398" t="n">
-        <v>2.648758648758649e-06</v>
+        <v>9.81021722e-05</v>
       </c>
       <c r="Q398" t="n">
-        <v>2.648759</v>
+        <v>98.1021852</v>
       </c>
       <c r="R398" t="n">
         <v>512.95</v>
@@ -26372,10 +26372,10 @@
         <v>2.687831</v>
       </c>
       <c r="P399" t="n">
-        <v>2.687830687830688e-06</v>
+        <v>9.95492847e-05</v>
       </c>
       <c r="Q399" t="n">
-        <v>2.687831</v>
+        <v>99.5492963</v>
       </c>
       <c r="R399" t="n">
         <v>456.34</v>
@@ -26437,10 +26437,10 @@
         <v>2.730159</v>
       </c>
       <c r="P400" t="n">
-        <v>2.73015873015873e-06</v>
+        <v>0.00010111699</v>
       </c>
       <c r="Q400" t="n">
-        <v>2.730159</v>
+        <v>101.117</v>
       </c>
       <c r="R400" t="n">
         <v>574.2</v>
@@ -26502,10 +26502,10 @@
         <v>2.768824</v>
       </c>
       <c r="P401" t="n">
-        <v>2.768823768823769e-06</v>
+        <v>0.000102549028</v>
       </c>
       <c r="Q401" t="n">
-        <v>2.768824</v>
+        <v>102.549037</v>
       </c>
       <c r="R401" t="n">
         <v>518.73</v>
@@ -26567,10 +26567,10 @@
         <v>2.808303</v>
       </c>
       <c r="P402" t="n">
-        <v>2.808302808302808e-06</v>
+        <v>0.000104011215</v>
       </c>
       <c r="Q402" t="n">
-        <v>2.808303</v>
+        <v>104.011222</v>
       </c>
       <c r="R402" t="n">
         <v>513.73</v>
@@ -26632,10 +26632,10 @@
         <v>2.845747</v>
       </c>
       <c r="P403" t="n">
-        <v>2.845746845746846e-06</v>
+        <v>0.000105398031</v>
       </c>
       <c r="Q403" t="n">
-        <v>2.845747</v>
+        <v>105.398037</v>
       </c>
       <c r="R403" t="n">
         <v>515.9400000000001</v>
@@ -26697,10 +26697,10 @@
         <v>2.873423</v>
       </c>
       <c r="P404" t="n">
-        <v>2.873422873422874e-06</v>
+        <v>0.000106423069</v>
       </c>
       <c r="Q404" t="n">
-        <v>2.873423</v>
+        <v>106.423074</v>
       </c>
       <c r="R404" t="n">
         <v>573.91</v>
@@ -26762,10 +26762,10 @@
         <v>2.900285</v>
       </c>
       <c r="P405" t="n">
-        <v>2.900284900284901e-06</v>
+        <v>0.000107417959</v>
       </c>
       <c r="Q405" t="n">
-        <v>2.900285</v>
+        <v>107.417963</v>
       </c>
       <c r="R405" t="n">
         <v>449.75</v>
@@ -26827,10 +26827,10 @@
         <v>2.862434</v>
       </c>
       <c r="P406" t="n">
-        <v>2.862433862433863e-06</v>
+        <v>0.000106016069</v>
       </c>
       <c r="Q406" t="n">
-        <v>2.862434</v>
+        <v>106.016074</v>
       </c>
       <c r="R406" t="n">
         <v>578.99</v>
@@ -26892,10 +26892,10 @@
         <v>2.82906</v>
       </c>
       <c r="P407" t="n">
-        <v>2.829059829059829e-06</v>
+        <v>0.000104779994</v>
       </c>
       <c r="Q407" t="n">
-        <v>2.82906</v>
+        <v>104.78</v>
       </c>
       <c r="R407" t="n">
         <v>519.23</v>
@@ -26957,10 +26957,10 @@
         <v>2.795686</v>
       </c>
       <c r="P408" t="n">
-        <v>2.795685795685796e-06</v>
+        <v>0.000103543918</v>
       </c>
       <c r="Q408" t="n">
-        <v>2.795686</v>
+        <v>103.543926</v>
       </c>
       <c r="R408" t="n">
         <v>517.64</v>
@@ -27022,10 +27022,10 @@
         <v>2.756614</v>
       </c>
       <c r="P409" t="n">
-        <v>2.756613756613756e-06</v>
+        <v>0.000102096806</v>
       </c>
       <c r="Q409" t="n">
-        <v>2.756614</v>
+        <v>102.096815</v>
       </c>
       <c r="R409" t="n">
         <v>514.48</v>
@@ -27087,10 +27087,10 @@
         <v>2.729345</v>
       </c>
       <c r="P410" t="n">
-        <v>2.72934472934473e-06</v>
+        <v>0.000101086842</v>
       </c>
       <c r="Q410" t="n">
-        <v>2.729345</v>
+        <v>101.086852</v>
       </c>
       <c r="R410" t="n">
         <v>516.6</v>
@@ -27152,10 +27152,10 @@
         <v>2.693529</v>
       </c>
       <c r="P411" t="n">
-        <v>2.693528693528694e-06</v>
+        <v>9.9760322e-05</v>
       </c>
       <c r="Q411" t="n">
-        <v>2.693529</v>
+        <v>99.7603333</v>
       </c>
       <c r="R411" t="n">
         <v>507.13</v>
@@ -27217,10 +27217,10 @@
         <v>2.663411</v>
       </c>
       <c r="P412" t="n">
-        <v>2.663410663410664e-06</v>
+        <v>9.86448394e-05</v>
       </c>
       <c r="Q412" t="n">
-        <v>2.663411</v>
+        <v>98.6448519</v>
       </c>
       <c r="R412" t="n">
         <v>515.96</v>
@@ -27282,10 +27282,10 @@
         <v>2.637363</v>
       </c>
       <c r="P413" t="n">
-        <v>2.637362637362637e-06</v>
+        <v>9.76800977e-05</v>
       </c>
       <c r="Q413" t="n">
-        <v>2.637363</v>
+        <v>97.6801111</v>
       </c>
       <c r="R413" t="n">
         <v>575.34</v>
@@ -27347,10 +27347,10 @@
         <v>2.608059</v>
       </c>
       <c r="P414" t="n">
-        <v>2.608058608058608e-06</v>
+        <v>9.65947633e-05</v>
       </c>
       <c r="Q414" t="n">
-        <v>2.608059</v>
+        <v>96.5947778</v>
       </c>
       <c r="R414" t="n">
         <v>456.69</v>
@@ -27412,10 +27412,10 @@
         <v>2.578755</v>
       </c>
       <c r="P415" t="n">
-        <v>2.578754578754579e-06</v>
+        <v>9.55094288e-05</v>
       </c>
       <c r="Q415" t="n">
-        <v>2.578755</v>
+        <v>95.5094444</v>
       </c>
       <c r="R415" t="n">
         <v>447.85</v>
@@ -27477,10 +27477,10 @@
         <v>2.555963</v>
       </c>
       <c r="P416" t="n">
-        <v>2.555962555962556e-06</v>
+        <v>9.46652799e-05</v>
       </c>
       <c r="Q416" t="n">
-        <v>2.555963</v>
+        <v>94.6652963</v>
       </c>
       <c r="R416" t="n">
         <v>509.06</v>
@@ -27542,10 +27542,10 @@
         <v>2.532357</v>
       </c>
       <c r="P417" t="n">
-        <v>2.532356532356532e-06</v>
+        <v>9.37909827e-05</v>
       </c>
       <c r="Q417" t="n">
-        <v>2.532357</v>
+        <v>93.791</v>
       </c>
       <c r="R417" t="n">
         <v>576.9299999999999</v>
@@ -27607,10 +27607,10 @@
         <v>2.512414</v>
       </c>
       <c r="P418" t="n">
-        <v>2.512413512413512e-06</v>
+        <v>9.30523523e-05</v>
       </c>
       <c r="Q418" t="n">
-        <v>2.512414</v>
+        <v>93.0523704</v>
       </c>
       <c r="R418" t="n">
         <v>574.33</v>
@@ -27672,10 +27672,10 @@
         <v>2.49247</v>
       </c>
       <c r="P419" t="n">
-        <v>2.492470492470492e-06</v>
+        <v>9.23137219e-05</v>
       </c>
       <c r="Q419" t="n">
-        <v>2.49247</v>
+        <v>92.3137037</v>
       </c>
       <c r="R419" t="n">
         <v>516.74</v>
@@ -27737,10 +27737,10 @@
         <v>2.474155</v>
       </c>
       <c r="P420" t="n">
-        <v>2.474155474155474e-06</v>
+        <v>9.16353879e-05</v>
       </c>
       <c r="Q420" t="n">
-        <v>2.474155</v>
+        <v>91.6353704</v>
       </c>
       <c r="R420" t="n">
         <v>395.04</v>
@@ -27802,10 +27802,10 @@
         <v>2.456654</v>
       </c>
       <c r="P421" t="n">
-        <v>2.456654456654457e-06</v>
+        <v>9.09872021e-05</v>
       </c>
       <c r="Q421" t="n">
-        <v>2.456654</v>
+        <v>90.9871852</v>
       </c>
       <c r="R421" t="n">
         <v>524.5700000000001</v>
@@ -27867,10 +27867,10 @@
         <v>2.440374</v>
       </c>
       <c r="P422" t="n">
-        <v>2.44037444037444e-06</v>
+        <v>9.03842385e-05</v>
       </c>
       <c r="Q422" t="n">
-        <v>2.440374</v>
+        <v>90.3842222</v>
       </c>
       <c r="R422" t="n">
         <v>452.18</v>
@@ -27932,10 +27932,10 @@
         <v>2.41921</v>
       </c>
       <c r="P423" t="n">
-        <v>2.419210419210419e-06</v>
+        <v>8.96003859e-05</v>
       </c>
       <c r="Q423" t="n">
-        <v>2.41921</v>
+        <v>89.6003704</v>
       </c>
       <c r="R423" t="n">
         <v>396.87</v>
@@ -27997,10 +27997,10 @@
         <v>2.40293</v>
       </c>
       <c r="P424" t="n">
-        <v>2.402930402930403e-06</v>
+        <v>8.89974223e-05</v>
       </c>
       <c r="Q424" t="n">
-        <v>2.40293</v>
+        <v>88.9974074</v>
       </c>
       <c r="R424" t="n">
         <v>465.99</v>
@@ -28062,10 +28062,10 @@
         <v>2.387057</v>
       </c>
       <c r="P425" t="n">
-        <v>2.387057387057387e-06</v>
+        <v>8.84095329e-05</v>
       </c>
       <c r="Q425" t="n">
-        <v>2.387057</v>
+        <v>88.4095185</v>
       </c>
       <c r="R425" t="n">
         <v>450.9</v>
@@ -28127,10 +28127,10 @@
         <v>2.381359</v>
       </c>
       <c r="P426" t="n">
-        <v>2.381359381359381e-06</v>
+        <v>8.81984956e-05</v>
       </c>
       <c r="Q426" t="n">
-        <v>2.381359</v>
+        <v>88.1984815</v>
       </c>
       <c r="R426" t="n">
         <v>573.27</v>
@@ -28192,10 +28192,10 @@
         <v>2.365079</v>
       </c>
       <c r="P427" t="n">
-        <v>2.365079365079365e-06</v>
+        <v>8.7595532e-05</v>
       </c>
       <c r="Q427" t="n">
-        <v>2.365079</v>
+        <v>87.5955185</v>
       </c>
       <c r="R427" t="n">
         <v>394.57</v>
@@ -28257,10 +28257,10 @@
         <v>2.358567</v>
       </c>
       <c r="P428" t="n">
-        <v>2.358567358567359e-06</v>
+        <v>8.73543466e-05</v>
       </c>
       <c r="Q428" t="n">
-        <v>2.358567</v>
+        <v>87.3543333</v>
       </c>
       <c r="R428" t="n">
         <v>463.11</v>
@@ -28322,10 +28322,10 @@
         <v>2.35409</v>
       </c>
       <c r="P429" t="n">
-        <v>2.354090354090354e-06</v>
+        <v>8.71885316e-05</v>
       </c>
       <c r="Q429" t="n">
-        <v>2.35409</v>
+        <v>87.1885185</v>
       </c>
       <c r="R429" t="n">
         <v>396.76</v>
@@ -28387,10 +28387,10 @@
         <v>2.350427</v>
       </c>
       <c r="P430" t="n">
-        <v>2.35042735042735e-06</v>
+        <v>8.70528648e-05</v>
       </c>
       <c r="Q430" t="n">
-        <v>2.350427</v>
+        <v>87.0528519</v>
       </c>
       <c r="R430" t="n">
         <v>529.02</v>
@@ -28452,10 +28452,10 @@
         <v>2.342287</v>
       </c>
       <c r="P431" t="n">
-        <v>2.342287342287342e-06</v>
+        <v>8.6751383e-05</v>
       </c>
       <c r="Q431" t="n">
-        <v>2.342287</v>
+        <v>86.7513704</v>
       </c>
       <c r="R431" t="n">
         <v>509.06</v>
@@ -28517,10 +28517,10 @@
         <v>2.342287</v>
       </c>
       <c r="P432" t="n">
-        <v>2.342287342287342e-06</v>
+        <v>8.6751383e-05</v>
       </c>
       <c r="Q432" t="n">
-        <v>2.342287</v>
+        <v>86.7513704</v>
       </c>
       <c r="R432" t="n">
         <v>459.19</v>
@@ -28582,10 +28582,10 @@
         <v>2.341066</v>
       </c>
       <c r="P433" t="n">
-        <v>2.341066341066341e-06</v>
+        <v>8.67061608e-05</v>
       </c>
       <c r="Q433" t="n">
-        <v>2.341066</v>
+        <v>86.7061481</v>
       </c>
       <c r="R433" t="n">
         <v>570.37</v>
@@ -28647,10 +28647,10 @@
         <v>2.34188</v>
       </c>
       <c r="P434" t="n">
-        <v>2.341880341880342e-06</v>
+        <v>8.6736309e-05</v>
       </c>
       <c r="Q434" t="n">
-        <v>2.34188</v>
+        <v>86.7362963</v>
       </c>
       <c r="R434" t="n">
         <v>518.3200000000001</v>
@@ -28712,10 +28712,10 @@
         <v>2.343508</v>
       </c>
       <c r="P435" t="n">
-        <v>2.343508343508343e-06</v>
+        <v>8.67966053e-05</v>
       </c>
       <c r="Q435" t="n">
-        <v>2.343508</v>
+        <v>86.7965926</v>
       </c>
       <c r="R435" t="n">
         <v>575.1</v>
